--- a/docs/大島 佑斗さん_新模擬案件_Bookshelf_要件シート.xlsx
+++ b/docs/大島 佑斗さん_新模擬案件_Bookshelf_要件シート.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{31957C62-DD6F-E542-ACD7-A3A4BD4FDD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CDB6BB-CEB7-504E-8812-2C182368C1DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="シート1 ターム内容" sheetId="1" r:id="rId1"/>
@@ -3647,59 +3647,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>選択肢：「in_progress」</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>デフォルト</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>「completed」</t>
-    </r>
-    <phoneticPr fontId="73"/>
-  </si>
-  <si>
-    <r>
       <t>notifications(Laravel</t>
     </r>
     <r>
@@ -11197,6 +11144,59 @@
     <t>$this-&gt;genres-&gt;map(fn ($genre) =&gt; [
                 'name' =&gt; $genre-&gt;name,
             ])</t>
+    <phoneticPr fontId="73"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>選択肢：「in_progress」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>デフォルト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「completed」「expired」</t>
+    </r>
     <phoneticPr fontId="73"/>
   </si>
 </sst>
@@ -15708,7 +15708,7 @@
       <c r="I6" s="254"/>
       <c r="J6" s="255"/>
       <c r="K6" s="256" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="13">
@@ -15733,7 +15733,7 @@
         <v>564</v>
       </c>
       <c r="K7" s="262" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="13">
@@ -15754,7 +15754,7 @@
       <c r="I8" s="258"/>
       <c r="J8" s="261"/>
       <c r="K8" s="262" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="13">
@@ -15777,7 +15777,7 @@
         <v>622</v>
       </c>
       <c r="K9" s="262" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="13">
@@ -15798,7 +15798,7 @@
         <v>573</v>
       </c>
       <c r="K10" s="262" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="13">
@@ -15819,7 +15819,7 @@
       <c r="I11" s="258"/>
       <c r="J11" s="261"/>
       <c r="K11" s="262" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="13">
@@ -15840,7 +15840,7 @@
         <v>576</v>
       </c>
       <c r="K12" s="262" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="13">
@@ -15861,7 +15861,7 @@
         <v>582</v>
       </c>
       <c r="K13" s="262" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="13">
@@ -15882,7 +15882,7 @@
         <v>582</v>
       </c>
       <c r="K14" s="262" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="13">
@@ -15899,7 +15899,7 @@
         <v>584</v>
       </c>
       <c r="K15" s="262" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13">
@@ -15916,7 +15916,7 @@
       <c r="I16" s="273"/>
       <c r="J16" s="274"/>
       <c r="K16" s="262" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="14">
@@ -15933,7 +15933,7 @@
       <c r="I17" s="254"/>
       <c r="J17" s="255"/>
       <c r="K17" s="287" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="13">
@@ -15956,7 +15956,7 @@
       <c r="I18" s="258"/>
       <c r="J18" s="261"/>
       <c r="K18" s="287" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="13">
@@ -15977,7 +15977,7 @@
       <c r="I19" s="258"/>
       <c r="J19" s="261"/>
       <c r="K19" s="287" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="13">
@@ -16000,7 +16000,7 @@
         <v>666</v>
       </c>
       <c r="K20" s="287" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="14">
@@ -16017,7 +16017,7 @@
       <c r="I21" s="254"/>
       <c r="J21" s="255"/>
       <c r="K21" s="287" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="13">
@@ -16042,7 +16042,7 @@
         <v>564</v>
       </c>
       <c r="K22" s="287" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="13">
@@ -16065,7 +16065,7 @@
         <v>675</v>
       </c>
       <c r="K23" s="287" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="13">
@@ -16088,7 +16088,7 @@
         <v>675</v>
       </c>
       <c r="K24" s="287" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="13">
@@ -16109,7 +16109,7 @@
       <c r="I25" s="258"/>
       <c r="J25" s="261"/>
       <c r="K25" s="287" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="13">
@@ -16132,7 +16132,7 @@
         <v>622</v>
       </c>
       <c r="K26" s="287" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="13">
@@ -16151,7 +16151,7 @@
       <c r="I27" s="258"/>
       <c r="J27" s="261"/>
       <c r="K27" s="287" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="13">
@@ -16170,7 +16170,7 @@
       <c r="I28" s="258"/>
       <c r="J28" s="261"/>
       <c r="K28" s="287" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="13">
@@ -16189,7 +16189,7 @@
       <c r="I29" s="258"/>
       <c r="J29" s="261"/>
       <c r="K29" s="320" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="13">
@@ -16210,7 +16210,7 @@
         <v>582</v>
       </c>
       <c r="K30" s="320" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="13">
@@ -16231,7 +16231,7 @@
         <v>582</v>
       </c>
       <c r="K31" s="320" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="14">
@@ -16248,7 +16248,7 @@
       <c r="I32" s="254"/>
       <c r="J32" s="255"/>
       <c r="K32" s="287" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="13">
@@ -16273,7 +16273,7 @@
         <v>564</v>
       </c>
       <c r="K33" s="287" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="13">
@@ -16296,7 +16296,7 @@
         <v>622</v>
       </c>
       <c r="K34" s="287" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="13">
@@ -16317,7 +16317,7 @@
       <c r="I35" s="258"/>
       <c r="J35" s="261"/>
       <c r="K35" s="287" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="13">
@@ -16338,7 +16338,7 @@
       <c r="I36" s="258"/>
       <c r="J36" s="261"/>
       <c r="K36" s="287" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="13">
@@ -16359,7 +16359,7 @@
       <c r="I37" s="258"/>
       <c r="J37" s="261"/>
       <c r="K37" s="287" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="13">
@@ -16380,7 +16380,7 @@
       <c r="I38" s="258"/>
       <c r="J38" s="261"/>
       <c r="K38" s="320" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="13">
@@ -16403,7 +16403,7 @@
         <v>683</v>
       </c>
       <c r="K39" s="320" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="13">
@@ -16420,7 +16420,7 @@
       <c r="I40" s="254"/>
       <c r="J40" s="255"/>
       <c r="K40" s="256" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="13">
@@ -16445,7 +16445,7 @@
         <v>564</v>
       </c>
       <c r="K41" s="262" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="14">
@@ -16470,7 +16470,7 @@
         <v>624</v>
       </c>
       <c r="K42" s="262" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="13">
@@ -16491,7 +16491,7 @@
       <c r="I43" s="258"/>
       <c r="J43" s="261"/>
       <c r="K43" s="262" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="13">
@@ -16512,7 +16512,7 @@
       <c r="I44" s="258"/>
       <c r="J44" s="261"/>
       <c r="K44" s="262" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="13">
@@ -16535,7 +16535,7 @@
         <v>622</v>
       </c>
       <c r="K45" s="262" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="14">
@@ -16558,7 +16558,7 @@
         <v>684</v>
       </c>
       <c r="K46" s="262" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="13">
@@ -16577,7 +16577,7 @@
       <c r="I47" s="258"/>
       <c r="J47" s="261"/>
       <c r="K47" s="262" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="13">
@@ -16596,7 +16596,7 @@
       <c r="I48" s="258"/>
       <c r="J48" s="261"/>
       <c r="K48" s="262" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="13">
@@ -16617,7 +16617,7 @@
         <v>582</v>
       </c>
       <c r="K49" s="262" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="13">
@@ -16638,7 +16638,7 @@
         <v>582</v>
       </c>
       <c r="K50" s="262" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="13">
@@ -16655,7 +16655,7 @@
       <c r="I51" s="254"/>
       <c r="J51" s="255"/>
       <c r="K51" s="256" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="13">
@@ -16680,7 +16680,7 @@
         <v>564</v>
       </c>
       <c r="K52" s="262" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="13">
@@ -16703,7 +16703,7 @@
         <v>622</v>
       </c>
       <c r="K53" s="262" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="13">
@@ -16724,7 +16724,7 @@
         <v>582</v>
       </c>
       <c r="K54" s="262" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="13">
@@ -16745,7 +16745,7 @@
         <v>582</v>
       </c>
       <c r="K55" s="262" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="13">
@@ -16762,7 +16762,7 @@
       <c r="I56" s="254"/>
       <c r="J56" s="255"/>
       <c r="K56" s="287" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="13">
@@ -16787,7 +16787,7 @@
         <v>564</v>
       </c>
       <c r="K57" s="287" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="14">
@@ -16812,7 +16812,7 @@
         <v>641</v>
       </c>
       <c r="K58" s="287" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="14">
@@ -16837,7 +16837,7 @@
         <v>656</v>
       </c>
       <c r="K59" s="287" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="13">
@@ -16858,7 +16858,7 @@
         <v>582</v>
       </c>
       <c r="K60" s="287" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="13">
@@ -16879,7 +16879,7 @@
         <v>582</v>
       </c>
       <c r="K61" s="320" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="14">
@@ -16898,7 +16898,7 @@
         <v>658</v>
       </c>
       <c r="K62" s="287" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="13">
@@ -16915,7 +16915,7 @@
       <c r="I63" s="254"/>
       <c r="J63" s="255"/>
       <c r="K63" s="256" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="13">
@@ -16940,7 +16940,7 @@
         <v>564</v>
       </c>
       <c r="K64" s="262" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="14">
@@ -16965,7 +16965,7 @@
         <v>641</v>
       </c>
       <c r="K65" s="262" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="14">
@@ -16990,7 +16990,7 @@
         <v>635</v>
       </c>
       <c r="K66" s="262" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="14">
@@ -17013,7 +17013,7 @@
         <v>638</v>
       </c>
       <c r="K67" s="262" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="13">
@@ -17034,7 +17034,7 @@
       <c r="I68" s="281"/>
       <c r="J68" s="283"/>
       <c r="K68" s="262" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="13">
@@ -17055,7 +17055,7 @@
         <v>582</v>
       </c>
       <c r="K69" s="262" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="13">
@@ -17064,7 +17064,7 @@
       <c r="C70" s="257"/>
       <c r="D70" s="13"/>
       <c r="E70" s="258" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F70" s="258" t="s">
         <v>572</v>
@@ -17093,7 +17093,7 @@
         <v>640</v>
       </c>
       <c r="K71" s="262" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="13">
@@ -17118,7 +17118,7 @@
         <v>564</v>
       </c>
       <c r="K72" s="262" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="13">
@@ -17143,7 +17143,7 @@
         <v>642</v>
       </c>
       <c r="K73" s="262" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="14">
@@ -17168,7 +17168,7 @@
         <v>639</v>
       </c>
       <c r="K74" s="262" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="13">
@@ -17189,7 +17189,7 @@
         <v>582</v>
       </c>
       <c r="K75" s="262" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="13">
@@ -17210,7 +17210,7 @@
         <v>582</v>
       </c>
       <c r="K76" s="262" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="14">
@@ -17228,7 +17228,7 @@
         <v>645</v>
       </c>
       <c r="K77" s="262" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="14">
@@ -17247,7 +17247,7 @@
         <v>651</v>
       </c>
       <c r="K78" s="287" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="13">
@@ -17272,7 +17272,7 @@
         <v>564</v>
       </c>
       <c r="K79" s="287" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="14">
@@ -17320,7 +17320,7 @@
         <v>647</v>
       </c>
       <c r="K81" s="287" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="13">
@@ -17341,7 +17341,7 @@
         <v>582</v>
       </c>
       <c r="K82" s="287" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="13">
@@ -17362,7 +17362,7 @@
         <v>582</v>
       </c>
       <c r="K83" s="287" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="14">
@@ -17380,7 +17380,7 @@
         <v>652</v>
       </c>
       <c r="K84" s="287" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="13">
@@ -17397,7 +17397,7 @@
       <c r="I85" s="322"/>
       <c r="J85" s="323"/>
       <c r="K85" s="287" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="13">
@@ -17422,7 +17422,7 @@
         <v>564</v>
       </c>
       <c r="K86" s="287" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="14">
@@ -17447,7 +17447,7 @@
         <v>699</v>
       </c>
       <c r="K87" s="287" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="13">
@@ -17472,7 +17472,7 @@
         <v>700</v>
       </c>
       <c r="K88" s="287" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="13">
@@ -17511,10 +17511,10 @@
       </c>
       <c r="I90" s="325"/>
       <c r="J90" s="327" t="s">
-        <v>701</v>
+        <v>1018</v>
       </c>
       <c r="K90" s="287" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="13">
@@ -17533,7 +17533,7 @@
       <c r="I91" s="325"/>
       <c r="J91" s="311"/>
       <c r="K91" s="320" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="13">
@@ -17554,7 +17554,7 @@
         <v>582</v>
       </c>
       <c r="K92" s="320" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="13">
@@ -17575,7 +17575,7 @@
         <v>582</v>
       </c>
       <c r="K93" s="320" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="14">
@@ -17594,7 +17594,7 @@
         <v>688</v>
       </c>
       <c r="K94" s="320" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="14">
@@ -17602,7 +17602,7 @@
       <c r="B95" s="285"/>
       <c r="C95" s="252"/>
       <c r="D95" s="321" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E95" s="322"/>
       <c r="F95" s="322"/>
@@ -17611,7 +17611,7 @@
       <c r="I95" s="322"/>
       <c r="J95" s="323"/>
       <c r="K95" s="287" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="13">
@@ -17636,7 +17636,7 @@
         <v>690</v>
       </c>
       <c r="K96" s="287" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="13">
@@ -17657,7 +17657,7 @@
       <c r="I97" s="325"/>
       <c r="J97" s="311"/>
       <c r="K97" s="287" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="13">
@@ -17701,7 +17701,7 @@
         <v>692</v>
       </c>
       <c r="K99" s="287" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="13">
@@ -17722,7 +17722,7 @@
       <c r="I100" s="325"/>
       <c r="J100" s="311"/>
       <c r="K100" s="320" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="13">
@@ -17743,7 +17743,7 @@
         <v>698</v>
       </c>
       <c r="K101" s="320" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="13">
@@ -17764,7 +17764,7 @@
         <v>582</v>
       </c>
       <c r="K102" s="320" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="13">
@@ -17785,7 +17785,7 @@
         <v>582</v>
       </c>
       <c r="K103" s="320" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="13">
@@ -17800,7 +17800,7 @@
       <c r="I104" s="56"/>
       <c r="J104" s="56"/>
       <c r="K104" s="285" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="13">
@@ -17817,7 +17817,7 @@
       <c r="I105" s="56"/>
       <c r="J105" s="56"/>
       <c r="K105" s="285" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="13">
@@ -17834,7 +17834,7 @@
       <c r="I106" s="56"/>
       <c r="J106" s="56"/>
       <c r="K106" s="285" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="13">
@@ -17851,7 +17851,7 @@
       <c r="I107" s="56"/>
       <c r="J107" s="56"/>
       <c r="K107" s="285" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="13">
@@ -17868,7 +17868,7 @@
       <c r="I108" s="56"/>
       <c r="J108" s="56"/>
       <c r="K108" s="285" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="13">
@@ -17885,117 +17885,117 @@
       <c r="I109" s="56"/>
       <c r="J109" s="56"/>
       <c r="K109" s="285" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="15.75" customHeight="1">
       <c r="K111" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="15.75" customHeight="1">
       <c r="K112" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="113" spans="11:11" ht="15.75" customHeight="1">
       <c r="K113" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="114" spans="11:11" ht="15.75" customHeight="1">
       <c r="K114" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="115" spans="11:11" ht="15.75" customHeight="1">
       <c r="K115" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="116" spans="11:11" ht="15.75" customHeight="1">
       <c r="K116" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="117" spans="11:11" ht="15.75" customHeight="1">
       <c r="K117" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="118" spans="11:11" ht="15.75" customHeight="1">
       <c r="K118" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="119" spans="11:11" ht="15.75" customHeight="1">
       <c r="K119" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="120" spans="11:11" ht="15.75" customHeight="1">
       <c r="K120" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="122" spans="11:11" ht="15.75" customHeight="1">
       <c r="K122" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="123" spans="11:11" ht="15.75" customHeight="1">
       <c r="K123" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="124" spans="11:11" ht="15.75" customHeight="1">
       <c r="K124" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="125" spans="11:11" ht="15.75" customHeight="1">
       <c r="K125" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="126" spans="11:11" ht="15.75" customHeight="1">
       <c r="K126" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="127" spans="11:11" ht="15.75" customHeight="1">
       <c r="K127" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="128" spans="11:11" ht="15.75" customHeight="1">
       <c r="K128" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="129" spans="11:11" ht="15.75" customHeight="1">
       <c r="K129" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="130" spans="11:11" ht="15.75" customHeight="1">
       <c r="K130" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="131" spans="11:11" ht="15.75" customHeight="1">
       <c r="K131" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="132" spans="11:11" ht="15.75" customHeight="1">
       <c r="K132" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="133" spans="11:11" ht="15.75" customHeight="1">
       <c r="K133" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
   </sheetData>
@@ -18098,10 +18098,10 @@
         <v>177</v>
       </c>
       <c r="E6" s="265" t="s">
+        <v>887</v>
+      </c>
+      <c r="F6" s="379" t="s">
         <v>888</v>
-      </c>
-      <c r="F6" s="379" t="s">
-        <v>889</v>
       </c>
       <c r="G6" s="265" t="s">
         <v>570</v>
@@ -18119,10 +18119,10 @@
         <v>177</v>
       </c>
       <c r="E7" s="266" t="s">
+        <v>899</v>
+      </c>
+      <c r="F7" s="384" t="s">
         <v>900</v>
-      </c>
-      <c r="F7" s="384" t="s">
-        <v>901</v>
       </c>
       <c r="G7" s="266" t="s">
         <v>570</v>
@@ -18137,13 +18137,13 @@
       <c r="B8" s="259"/>
       <c r="C8" s="259"/>
       <c r="D8" s="267" t="s">
+        <v>924</v>
+      </c>
+      <c r="E8" s="267" t="s">
+        <v>887</v>
+      </c>
+      <c r="F8" s="397" t="s">
         <v>925</v>
-      </c>
-      <c r="E8" s="267" t="s">
-        <v>888</v>
-      </c>
-      <c r="F8" s="397" t="s">
-        <v>926</v>
       </c>
       <c r="G8" s="267" t="s">
         <v>570</v>
@@ -18161,10 +18161,10 @@
         <v>578</v>
       </c>
       <c r="E9" s="266" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F9" s="384" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G9" s="266" t="s">
         <v>570</v>
@@ -18182,7 +18182,7 @@
         <v>581</v>
       </c>
       <c r="E10" s="267" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F10" s="267" t="s">
         <v>463</v>
@@ -18210,7 +18210,7 @@
       <c r="A12" s="139"/>
       <c r="B12" s="259"/>
       <c r="C12" s="260" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D12" s="259"/>
       <c r="E12" s="259"/>
@@ -18251,7 +18251,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="264" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F15" s="259"/>
       <c r="G15" s="259"/>
@@ -18263,10 +18263,10 @@
       <c r="B16" s="259"/>
       <c r="C16" s="259"/>
       <c r="D16" s="265" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E16" s="265" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F16" s="259"/>
       <c r="G16" s="259"/>
@@ -18278,7 +18278,7 @@
       <c r="B17" s="259"/>
       <c r="C17" s="259"/>
       <c r="D17" s="265" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E17" s="265" t="s">
         <v>177</v>
@@ -18308,10 +18308,10 @@
       <c r="B19" s="259"/>
       <c r="C19" s="259"/>
       <c r="D19" s="265" t="s">
+        <v>870</v>
+      </c>
+      <c r="E19" s="265" t="s">
         <v>871</v>
-      </c>
-      <c r="E19" s="265" t="s">
-        <v>872</v>
       </c>
       <c r="F19" s="259"/>
       <c r="G19" s="259"/>
@@ -18326,7 +18326,7 @@
         <v>479</v>
       </c>
       <c r="E20" s="379" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F20" s="259"/>
       <c r="G20" s="259"/>
@@ -18349,7 +18349,7 @@
       <c r="B22" s="259"/>
       <c r="C22" s="259"/>
       <c r="D22" s="376" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E22" s="259"/>
       <c r="F22" s="259"/>
@@ -18362,19 +18362,19 @@
       <c r="B23" s="259"/>
       <c r="C23" s="259"/>
       <c r="D23" s="377" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E23" s="377" t="s">
         <v>553</v>
       </c>
       <c r="F23" s="377" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G23" s="377" t="s">
         <v>479</v>
       </c>
       <c r="H23" s="377" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="I23" s="259"/>
     </row>
@@ -18383,19 +18383,19 @@
       <c r="B24" s="259"/>
       <c r="C24" s="259"/>
       <c r="D24" s="265" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E24" s="265" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F24" s="265" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G24" s="379" t="s">
+        <v>893</v>
+      </c>
+      <c r="H24" s="100" t="s">
         <v>894</v>
-      </c>
-      <c r="H24" s="100" t="s">
-        <v>895</v>
       </c>
       <c r="I24" s="259"/>
     </row>
@@ -18404,19 +18404,19 @@
       <c r="B25" s="259"/>
       <c r="C25" s="259"/>
       <c r="D25" s="265" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E25" s="265" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F25" s="265" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G25" s="379" t="s">
+        <v>895</v>
+      </c>
+      <c r="H25" s="380" t="s">
         <v>896</v>
-      </c>
-      <c r="H25" s="380" t="s">
-        <v>897</v>
       </c>
       <c r="I25" s="259"/>
     </row>
@@ -18425,16 +18425,16 @@
       <c r="B26" s="259"/>
       <c r="C26" s="259"/>
       <c r="D26" s="265" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E26" s="265" t="s">
+        <v>876</v>
+      </c>
+      <c r="F26" s="265" t="s">
         <v>877</v>
       </c>
-      <c r="F26" s="265" t="s">
-        <v>878</v>
-      </c>
       <c r="G26" s="381" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H26" s="100">
         <v>2</v>
@@ -18446,16 +18446,16 @@
       <c r="B27" s="259"/>
       <c r="C27" s="259"/>
       <c r="D27" s="265" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E27" s="265" t="s">
+        <v>880</v>
+      </c>
+      <c r="F27" s="265" t="s">
+        <v>877</v>
+      </c>
+      <c r="G27" s="265" t="s">
         <v>881</v>
-      </c>
-      <c r="F27" s="265" t="s">
-        <v>878</v>
-      </c>
-      <c r="G27" s="265" t="s">
-        <v>882</v>
       </c>
       <c r="H27" s="100">
         <v>20</v>
@@ -18478,7 +18478,7 @@
       <c r="B29" s="259"/>
       <c r="C29" s="259"/>
       <c r="D29" s="378" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E29" s="259"/>
       <c r="F29" s="259"/>
@@ -18491,13 +18491,13 @@
       <c r="B30" s="259"/>
       <c r="C30" s="259"/>
       <c r="D30" s="377" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E30" s="377" t="s">
         <v>479</v>
       </c>
       <c r="F30" s="377" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G30" s="259"/>
       <c r="H30" s="259"/>
@@ -18508,13 +18508,13 @@
       <c r="B31" s="259"/>
       <c r="C31" s="259"/>
       <c r="D31" s="265" t="s">
+        <v>885</v>
+      </c>
+      <c r="E31" s="265" t="s">
         <v>886</v>
       </c>
-      <c r="E31" s="265" t="s">
-        <v>887</v>
-      </c>
       <c r="F31" s="265" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G31" s="382"/>
       <c r="H31" s="259"/>
@@ -18525,13 +18525,13 @@
       <c r="B32" s="259"/>
       <c r="C32" s="259"/>
       <c r="D32" s="265" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E32" s="381" t="s">
+        <v>943</v>
+      </c>
+      <c r="F32" s="265" t="s">
         <v>944</v>
-      </c>
-      <c r="F32" s="265" t="s">
-        <v>945</v>
       </c>
       <c r="G32" s="259"/>
       <c r="H32" s="259"/>
@@ -18553,7 +18553,7 @@
       <c r="B34" s="259"/>
       <c r="C34" s="259"/>
       <c r="D34" s="378" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E34" s="259"/>
       <c r="F34" s="259"/>
@@ -18653,7 +18653,7 @@
       <c r="A43" s="139"/>
       <c r="B43" s="259"/>
       <c r="C43" s="260" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D43" s="259"/>
       <c r="E43" s="259"/>
@@ -18667,7 +18667,7 @@
       <c r="B44" s="259"/>
       <c r="C44" s="259"/>
       <c r="D44" s="385" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E44" s="259"/>
       <c r="F44" s="259"/>
@@ -18694,7 +18694,7 @@
         <v>5</v>
       </c>
       <c r="E46" s="264" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F46" s="259"/>
       <c r="G46" s="259"/>
@@ -18706,10 +18706,10 @@
       <c r="B47" s="259"/>
       <c r="C47" s="259"/>
       <c r="D47" s="265" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E47" s="265" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F47" s="259"/>
       <c r="G47" s="259"/>
@@ -18721,7 +18721,7 @@
       <c r="B48" s="259"/>
       <c r="C48" s="259"/>
       <c r="D48" s="265" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E48" s="265" t="s">
         <v>177</v>
@@ -18751,10 +18751,10 @@
       <c r="B50" s="259"/>
       <c r="C50" s="259"/>
       <c r="D50" s="265" t="s">
+        <v>870</v>
+      </c>
+      <c r="E50" s="265" t="s">
         <v>871</v>
-      </c>
-      <c r="E50" s="265" t="s">
-        <v>872</v>
       </c>
       <c r="F50" s="259"/>
       <c r="G50" s="259"/>
@@ -18769,7 +18769,7 @@
         <v>479</v>
       </c>
       <c r="E51" s="379" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F51" s="259"/>
       <c r="G51" s="259"/>
@@ -18792,7 +18792,7 @@
       <c r="B53" s="259"/>
       <c r="C53" s="259"/>
       <c r="D53" s="376" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E53" s="259"/>
       <c r="F53" s="259"/>
@@ -18805,19 +18805,19 @@
       <c r="B54" s="259"/>
       <c r="C54" s="259"/>
       <c r="D54" s="377" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E54" s="377" t="s">
         <v>553</v>
       </c>
       <c r="F54" s="377" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G54" s="377" t="s">
         <v>479</v>
       </c>
       <c r="H54" s="377" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="I54" s="259"/>
     </row>
@@ -18826,16 +18826,16 @@
       <c r="B55" s="259"/>
       <c r="C55" s="259"/>
       <c r="D55" s="265" t="s">
+        <v>905</v>
+      </c>
+      <c r="E55" s="265" t="s">
+        <v>910</v>
+      </c>
+      <c r="F55" s="381" t="s">
         <v>906</v>
       </c>
-      <c r="E55" s="265" t="s">
-        <v>911</v>
-      </c>
-      <c r="F55" s="381" t="s">
+      <c r="G55" s="379" t="s">
         <v>907</v>
-      </c>
-      <c r="G55" s="379" t="s">
-        <v>908</v>
       </c>
       <c r="H55" s="100">
         <v>1</v>
@@ -18858,7 +18858,7 @@
       <c r="B57" s="259"/>
       <c r="C57" s="259"/>
       <c r="D57" s="378" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E57" s="259"/>
       <c r="F57" s="259"/>
@@ -18871,13 +18871,13 @@
       <c r="B58" s="259"/>
       <c r="C58" s="259"/>
       <c r="D58" s="377" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E58" s="377" t="s">
         <v>479</v>
       </c>
       <c r="F58" s="377" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G58" s="259"/>
       <c r="H58" s="259"/>
@@ -18888,13 +18888,13 @@
       <c r="B59" s="259"/>
       <c r="C59" s="259"/>
       <c r="D59" s="265" t="s">
+        <v>885</v>
+      </c>
+      <c r="E59" s="265" t="s">
         <v>886</v>
       </c>
-      <c r="E59" s="265" t="s">
-        <v>887</v>
-      </c>
       <c r="F59" s="265" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G59" s="382"/>
       <c r="H59" s="259"/>
@@ -18905,13 +18905,13 @@
       <c r="B60" s="259"/>
       <c r="C60" s="259"/>
       <c r="D60" s="265" t="s">
+        <v>908</v>
+      </c>
+      <c r="E60" s="265" t="s">
         <v>909</v>
       </c>
-      <c r="E60" s="265" t="s">
-        <v>910</v>
-      </c>
       <c r="F60" s="265" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G60" s="259"/>
       <c r="H60" s="259"/>
@@ -18933,7 +18933,7 @@
       <c r="B62" s="259"/>
       <c r="C62" s="259"/>
       <c r="D62" s="378" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E62" s="259"/>
       <c r="F62" s="259"/>
@@ -19022,7 +19022,7 @@
       <c r="A70" s="139"/>
       <c r="B70" s="259"/>
       <c r="C70" s="260" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D70" s="259"/>
       <c r="E70" s="259"/>
@@ -19063,7 +19063,7 @@
         <v>5</v>
       </c>
       <c r="E73" s="400" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F73" s="259"/>
       <c r="G73" s="259"/>
@@ -19075,10 +19075,10 @@
       <c r="B74" s="259"/>
       <c r="C74" s="259"/>
       <c r="D74" s="265" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E74" s="399" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F74" s="259"/>
       <c r="G74" s="259"/>
@@ -19090,10 +19090,10 @@
       <c r="B75" s="259"/>
       <c r="C75" s="259"/>
       <c r="D75" s="265" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E75" s="265" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F75" s="259"/>
       <c r="G75" s="259"/>
@@ -19108,7 +19108,7 @@
         <v>396</v>
       </c>
       <c r="E76" s="265" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F76" s="259"/>
       <c r="G76" s="259"/>
@@ -19120,10 +19120,10 @@
       <c r="B77" s="259"/>
       <c r="C77" s="259"/>
       <c r="D77" s="265" t="s">
+        <v>870</v>
+      </c>
+      <c r="E77" s="265" t="s">
         <v>871</v>
-      </c>
-      <c r="E77" s="265" t="s">
-        <v>872</v>
       </c>
       <c r="F77" s="259"/>
       <c r="G77" s="259"/>
@@ -19138,7 +19138,7 @@
         <v>479</v>
       </c>
       <c r="E78" s="379" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F78" s="387"/>
       <c r="G78" s="259"/>
@@ -19161,7 +19161,7 @@
       <c r="B80" s="259"/>
       <c r="C80" s="259"/>
       <c r="D80" s="388" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E80" s="259"/>
       <c r="F80" s="259"/>
@@ -19174,13 +19174,13 @@
       <c r="B81" s="259"/>
       <c r="C81" s="259"/>
       <c r="D81" s="377" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E81" s="377" t="s">
         <v>553</v>
       </c>
       <c r="F81" s="377" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G81" s="389" t="s">
         <v>479</v>
@@ -19196,13 +19196,13 @@
         <v>625</v>
       </c>
       <c r="E82" s="265" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F82" s="265" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G82" s="403" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H82" s="393">
         <v>5</v>
@@ -19214,16 +19214,16 @@
       <c r="B83" s="259"/>
       <c r="C83" s="259"/>
       <c r="D83" s="265" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E83" s="265" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F83" s="265" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G83" s="403" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H83" s="393">
         <v>5</v>
@@ -19235,16 +19235,16 @@
       <c r="B84" s="259"/>
       <c r="C84" s="259"/>
       <c r="D84" s="265" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E84" s="265" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F84" s="265" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G84" s="402" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H84" s="393">
         <v>5</v>
@@ -19256,16 +19256,16 @@
       <c r="B85" s="259"/>
       <c r="C85" s="259"/>
       <c r="D85" s="265" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E85" s="265" t="s">
         <v>614</v>
       </c>
       <c r="F85" s="265" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G85" s="403" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H85" s="393">
         <v>5</v>
@@ -19277,16 +19277,16 @@
       <c r="B86" s="259"/>
       <c r="C86" s="259"/>
       <c r="D86" s="265" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E86" s="265" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F86" s="265" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G86" s="403" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H86" s="393">
         <v>5</v>
@@ -19298,16 +19298,16 @@
       <c r="B87" s="259"/>
       <c r="C87" s="259"/>
       <c r="D87" s="265" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E87" s="265" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F87" s="265" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G87" s="401" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H87" s="393">
         <v>5</v>
@@ -19319,16 +19319,16 @@
       <c r="B88" s="259"/>
       <c r="C88" s="259"/>
       <c r="D88" s="265" t="s">
+        <v>932</v>
+      </c>
+      <c r="E88" s="265" t="s">
         <v>933</v>
       </c>
-      <c r="E88" s="265" t="s">
-        <v>934</v>
-      </c>
       <c r="F88" s="265" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G88" s="403" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H88" s="393">
         <v>5</v>
@@ -19351,7 +19351,7 @@
       <c r="B90" s="259"/>
       <c r="C90" s="259"/>
       <c r="D90" s="378" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E90" s="259"/>
       <c r="F90" s="259"/>
@@ -19364,13 +19364,13 @@
       <c r="B91" s="259"/>
       <c r="C91" s="259"/>
       <c r="D91" s="377" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E91" s="377" t="s">
         <v>479</v>
       </c>
       <c r="F91" s="377" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G91" s="259"/>
       <c r="H91" s="259"/>
@@ -19381,13 +19381,13 @@
       <c r="B92" s="259"/>
       <c r="C92" s="259"/>
       <c r="D92" s="265" t="s">
+        <v>917</v>
+      </c>
+      <c r="E92" s="265" t="s">
         <v>918</v>
       </c>
-      <c r="E92" s="265" t="s">
-        <v>919</v>
-      </c>
       <c r="F92" s="265" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G92" s="259"/>
       <c r="H92" s="259"/>
@@ -19398,13 +19398,13 @@
       <c r="B93" s="259"/>
       <c r="C93" s="259"/>
       <c r="D93" s="265" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E93" s="381" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F93" s="265" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G93" s="259"/>
       <c r="H93" s="259"/>
@@ -19415,13 +19415,13 @@
       <c r="B94" s="259"/>
       <c r="C94" s="259"/>
       <c r="D94" s="265" t="s">
+        <v>920</v>
+      </c>
+      <c r="E94" s="265" t="s">
         <v>921</v>
       </c>
-      <c r="E94" s="265" t="s">
+      <c r="F94" s="265" t="s">
         <v>922</v>
-      </c>
-      <c r="F94" s="265" t="s">
-        <v>923</v>
       </c>
       <c r="G94" s="259"/>
       <c r="H94" s="259"/>
@@ -19432,7 +19432,7 @@
       <c r="B95" s="259"/>
       <c r="C95" s="259"/>
       <c r="D95" s="259" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E95" s="259"/>
       <c r="F95" s="259"/>
@@ -19466,7 +19466,7 @@
       <c r="A98" s="139"/>
       <c r="C98" s="259"/>
       <c r="D98" s="378" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E98" s="259"/>
       <c r="F98" s="259"/>
@@ -19544,7 +19544,7 @@
       <c r="A105" s="139"/>
       <c r="B105" s="259"/>
       <c r="C105" s="260" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D105" s="259"/>
       <c r="E105" s="259"/>
@@ -19558,7 +19558,7 @@
       <c r="B106" s="259"/>
       <c r="C106" s="259"/>
       <c r="D106" s="385" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E106" s="259"/>
       <c r="F106" s="259"/>
@@ -19585,7 +19585,7 @@
         <v>5</v>
       </c>
       <c r="E108" s="264" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F108" s="259"/>
       <c r="G108" s="259"/>
@@ -19597,10 +19597,10 @@
       <c r="B109" s="259"/>
       <c r="C109" s="259"/>
       <c r="D109" s="265" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E109" s="265" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F109" s="259"/>
       <c r="G109" s="259"/>
@@ -19612,10 +19612,10 @@
       <c r="B110" s="259"/>
       <c r="C110" s="259"/>
       <c r="D110" s="265" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E110" s="265" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F110" s="259"/>
       <c r="G110" s="259"/>
@@ -19630,7 +19630,7 @@
         <v>396</v>
       </c>
       <c r="E111" s="406" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F111" s="259"/>
       <c r="G111" s="259"/>
@@ -19642,10 +19642,10 @@
       <c r="B112" s="259"/>
       <c r="C112" s="259"/>
       <c r="D112" s="403" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E112" s="408" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F112" s="259"/>
       <c r="G112" s="259"/>
@@ -19660,7 +19660,7 @@
         <v>479</v>
       </c>
       <c r="E113" s="407" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F113" s="387"/>
       <c r="G113" s="259"/>
@@ -19672,7 +19672,7 @@
       <c r="B114" s="259"/>
       <c r="C114" s="259"/>
       <c r="D114" s="410" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E114" s="259"/>
       <c r="F114" s="259"/>
@@ -19696,7 +19696,7 @@
       <c r="B116" s="259"/>
       <c r="C116" s="259"/>
       <c r="D116" s="378" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E116" s="259"/>
       <c r="F116" s="259"/>
@@ -19709,13 +19709,13 @@
       <c r="B117" s="259"/>
       <c r="C117" s="259"/>
       <c r="D117" s="377" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E117" s="377" t="s">
         <v>553</v>
       </c>
       <c r="F117" s="389" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G117" s="404"/>
       <c r="H117" s="392"/>
@@ -19726,13 +19726,13 @@
       <c r="B118" s="259"/>
       <c r="C118" s="259"/>
       <c r="D118" s="265" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E118" s="265" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F118" s="402" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G118" s="409"/>
       <c r="H118" s="405"/>
@@ -19743,13 +19743,13 @@
       <c r="B119" s="259"/>
       <c r="C119" s="259"/>
       <c r="D119" s="265" t="s">
+        <v>908</v>
+      </c>
+      <c r="E119" s="265" t="s">
         <v>909</v>
       </c>
-      <c r="E119" s="265" t="s">
-        <v>910</v>
-      </c>
       <c r="F119" s="402" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G119" s="409"/>
       <c r="H119" s="405"/>
@@ -19760,13 +19760,13 @@
       <c r="B120" s="259"/>
       <c r="C120" s="259"/>
       <c r="D120" s="265" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E120" s="265" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F120" s="402" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G120" s="409"/>
       <c r="H120" s="405"/>
@@ -19777,13 +19777,13 @@
       <c r="B121" s="259"/>
       <c r="C121" s="259"/>
       <c r="D121" s="265" t="s">
+        <v>920</v>
+      </c>
+      <c r="E121" s="265" t="s">
         <v>921</v>
       </c>
-      <c r="E121" s="265" t="s">
-        <v>922</v>
-      </c>
       <c r="F121" s="402" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G121" s="409"/>
       <c r="H121" s="405"/>
@@ -19794,13 +19794,13 @@
       <c r="B122" s="259"/>
       <c r="C122" s="259"/>
       <c r="D122" s="265" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E122" s="379" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F122" s="402" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G122" s="409"/>
       <c r="H122" s="405"/>
@@ -19821,7 +19821,7 @@
       <c r="A124" s="139"/>
       <c r="C124" s="259"/>
       <c r="D124" s="388" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E124" s="259"/>
       <c r="F124" s="259"/>
@@ -19910,7 +19910,7 @@
       <c r="A132" s="139"/>
       <c r="B132" s="259"/>
       <c r="C132" s="260" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D132" s="259"/>
       <c r="E132" s="259"/>
@@ -19951,7 +19951,7 @@
         <v>5</v>
       </c>
       <c r="E135" s="264" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F135" s="259"/>
       <c r="G135" s="259"/>
@@ -19963,10 +19963,10 @@
       <c r="B136" s="259"/>
       <c r="C136" s="259"/>
       <c r="D136" s="265" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E136" s="265" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F136" s="259"/>
       <c r="G136" s="259"/>
@@ -19978,7 +19978,7 @@
       <c r="B137" s="259"/>
       <c r="C137" s="259"/>
       <c r="D137" s="265" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E137" s="265" t="s">
         <v>581</v>
@@ -19996,7 +19996,7 @@
         <v>396</v>
       </c>
       <c r="E138" s="406" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F138" s="259"/>
       <c r="G138" s="259"/>
@@ -20008,10 +20008,10 @@
       <c r="B139" s="259"/>
       <c r="C139" s="259"/>
       <c r="D139" s="402" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="E139" s="420" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F139" s="259"/>
       <c r="G139" s="259"/>
@@ -20026,7 +20026,7 @@
         <v>479</v>
       </c>
       <c r="E140" s="419" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F140" s="387"/>
       <c r="G140" s="259"/>
@@ -20049,7 +20049,7 @@
       <c r="B142" s="259"/>
       <c r="C142" s="259"/>
       <c r="D142" s="378" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E142" s="259"/>
       <c r="F142" s="259"/>
@@ -20062,13 +20062,13 @@
       <c r="B143" s="259"/>
       <c r="C143" s="259"/>
       <c r="D143" s="377" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E143" s="377" t="s">
         <v>479</v>
       </c>
       <c r="F143" s="377" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G143" s="259"/>
       <c r="H143" s="259"/>
@@ -20079,13 +20079,13 @@
       <c r="B144" s="259"/>
       <c r="C144" s="259"/>
       <c r="D144" s="265" t="s">
+        <v>966</v>
+      </c>
+      <c r="E144" s="265" t="s">
         <v>967</v>
       </c>
-      <c r="E144" s="265" t="s">
+      <c r="F144" s="265" t="s">
         <v>968</v>
-      </c>
-      <c r="F144" s="265" t="s">
-        <v>969</v>
       </c>
       <c r="G144" s="259"/>
       <c r="H144" s="259"/>
@@ -20096,13 +20096,13 @@
       <c r="B145" s="259"/>
       <c r="C145" s="259"/>
       <c r="D145" s="265" t="s">
+        <v>908</v>
+      </c>
+      <c r="E145" s="265" t="s">
         <v>909</v>
       </c>
-      <c r="E145" s="265" t="s">
-        <v>910</v>
-      </c>
       <c r="F145" s="265" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G145" s="259"/>
       <c r="H145" s="259"/>
@@ -20113,13 +20113,13 @@
       <c r="B146" s="259"/>
       <c r="C146" s="259"/>
       <c r="D146" s="265" t="s">
+        <v>920</v>
+      </c>
+      <c r="E146" s="265" t="s">
         <v>921</v>
       </c>
-      <c r="E146" s="265" t="s">
-        <v>922</v>
-      </c>
       <c r="F146" s="265" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G146" s="259"/>
       <c r="H146" s="259"/>
@@ -20130,13 +20130,13 @@
       <c r="B147" s="259"/>
       <c r="C147" s="259"/>
       <c r="D147" s="399" t="s">
+        <v>951</v>
+      </c>
+      <c r="E147" s="407" t="s">
+        <v>971</v>
+      </c>
+      <c r="F147" s="399" t="s">
         <v>952</v>
-      </c>
-      <c r="E147" s="407" t="s">
-        <v>972</v>
-      </c>
-      <c r="F147" s="399" t="s">
-        <v>953</v>
       </c>
       <c r="G147" s="259"/>
       <c r="H147" s="259"/>
@@ -20157,7 +20157,7 @@
       <c r="A149" s="139"/>
       <c r="C149" s="259"/>
       <c r="D149" s="378" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E149" s="259"/>
       <c r="F149" s="259"/>
@@ -20244,31 +20244,31 @@
         <v>5</v>
       </c>
       <c r="E157" s="264" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15.75" customHeight="1">
       <c r="D158" s="265" t="s">
+        <v>973</v>
+      </c>
+      <c r="E158" s="265" t="s">
         <v>974</v>
-      </c>
-      <c r="E158" s="265" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="32">
       <c r="D159" s="265" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E159" s="265" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15.75" customHeight="1">
       <c r="D160" s="265" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E160" s="265" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="161" spans="3:6" ht="15.75" customHeight="1">
@@ -20277,13 +20277,13 @@
     </row>
     <row r="162" spans="3:6" ht="15.75" customHeight="1">
       <c r="D162" s="378" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E162" s="259"/>
     </row>
     <row r="163" spans="3:6" ht="15.75" customHeight="1">
       <c r="D163" s="411" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E163" s="412" t="s">
         <v>553</v>
@@ -20291,63 +20291,63 @@
     </row>
     <row r="164" spans="3:6" ht="15.75" customHeight="1">
       <c r="D164" s="413" t="s">
+        <v>978</v>
+      </c>
+      <c r="E164" s="414" t="s">
         <v>979</v>
-      </c>
-      <c r="E164" s="414" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="165" spans="3:6" ht="15.75" customHeight="1">
       <c r="D165" s="415" t="s">
+        <v>980</v>
+      </c>
+      <c r="E165" s="416" t="s">
         <v>981</v>
-      </c>
-      <c r="E165" s="416" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="166" spans="3:6" ht="15.75" customHeight="1">
       <c r="D166" s="415" t="s">
+        <v>982</v>
+      </c>
+      <c r="E166" s="416" t="s">
         <v>983</v>
-      </c>
-      <c r="E166" s="416" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="167" spans="3:6" ht="15.75" customHeight="1">
       <c r="D167" s="415" t="s">
+        <v>984</v>
+      </c>
+      <c r="E167" s="416" t="s">
         <v>985</v>
-      </c>
-      <c r="E167" s="416" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="168" spans="3:6" ht="15.75" customHeight="1">
       <c r="D168" s="415" t="s">
+        <v>986</v>
+      </c>
+      <c r="E168" s="416" t="s">
         <v>987</v>
-      </c>
-      <c r="E168" s="416" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="169" spans="3:6" ht="15.75" customHeight="1">
       <c r="D169" s="415" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E169" s="416" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="170" spans="3:6" ht="15.75" customHeight="1">
       <c r="D170" s="417" t="s">
+        <v>989</v>
+      </c>
+      <c r="E170" s="418" t="s">
         <v>990</v>
-      </c>
-      <c r="E170" s="418" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="173" spans="3:6" ht="15.75" customHeight="1">
       <c r="C173" s="260" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D173" s="259"/>
       <c r="E173" s="259"/>
@@ -20356,7 +20356,7 @@
     <row r="174" spans="3:6" ht="15.75" customHeight="1">
       <c r="C174" s="259"/>
       <c r="D174" s="378" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E174" s="259"/>
       <c r="F174" s="259"/>
@@ -20364,78 +20364,78 @@
     <row r="175" spans="3:6" ht="15.75" customHeight="1">
       <c r="C175" s="259"/>
       <c r="D175" s="377" t="s">
+        <v>996</v>
+      </c>
+      <c r="E175" s="377" t="s">
         <v>997</v>
       </c>
-      <c r="E175" s="377" t="s">
+      <c r="F175" s="377" t="s">
         <v>998</v>
-      </c>
-      <c r="F175" s="377" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="176" spans="3:6" ht="48">
       <c r="C176" s="259"/>
       <c r="D176" s="265" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E176" s="100">
         <v>404</v>
       </c>
       <c r="F176" s="265" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="177" spans="3:7" ht="15.75" customHeight="1">
       <c r="C177" s="259"/>
       <c r="D177" s="265" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E177" s="100">
         <v>422</v>
       </c>
       <c r="F177" s="265" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="178" spans="3:7" ht="15.75" customHeight="1">
       <c r="C178" s="259"/>
       <c r="D178" s="265" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E178" s="100">
         <v>401</v>
       </c>
       <c r="F178" s="265" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="179" spans="3:7" ht="32">
       <c r="C179" s="259"/>
       <c r="D179" s="399" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E179" s="421">
         <v>403</v>
       </c>
       <c r="F179" s="399" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="181" spans="3:7" ht="15.75" customHeight="1">
       <c r="C181" s="260" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="182" spans="3:7" ht="15.75" customHeight="1">
       <c r="D182" s="422" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E182" s="390"/>
       <c r="F182" s="390"/>
     </row>
     <row r="183" spans="3:7" ht="15.75" customHeight="1">
       <c r="D183" s="425" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E183" s="426"/>
       <c r="F183" s="426"/>
@@ -20443,33 +20443,33 @@
     </row>
     <row r="185" spans="3:7" ht="15.75" customHeight="1">
       <c r="D185" s="264" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E185" s="264" t="s">
         <v>1005</v>
       </c>
-      <c r="E185" s="264" t="s">
+      <c r="F185" s="264" t="s">
         <v>1006</v>
-      </c>
-      <c r="F185" s="264" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="186" spans="3:7" ht="15.75" customHeight="1">
       <c r="D186" s="265" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E186" s="265" t="s">
         <v>560</v>
       </c>
       <c r="F186" s="265" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="187" spans="3:7" ht="15.75" customHeight="1">
       <c r="D187" s="265"/>
       <c r="E187" s="265" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F187" s="265" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="188" spans="3:7" ht="15.75" customHeight="1">
@@ -20478,7 +20478,7 @@
         <v>626</v>
       </c>
       <c r="F188" s="265" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="189" spans="3:7" ht="15.75" customHeight="1">
@@ -20487,7 +20487,7 @@
         <v>627</v>
       </c>
       <c r="F189" s="265" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="190" spans="3:7" ht="15.75" customHeight="1">
@@ -20496,7 +20496,7 @@
         <v>629</v>
       </c>
       <c r="F190" s="265" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="191" spans="3:7" ht="15.75" customHeight="1">
@@ -20505,7 +20505,7 @@
         <v>630</v>
       </c>
       <c r="F191" s="265" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="192" spans="3:7" ht="48">
@@ -20514,7 +20514,7 @@
         <v>617</v>
       </c>
       <c r="F192" s="265" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
   </sheetData>
@@ -33423,7 +33423,7 @@
         <v>291</v>
       </c>
       <c r="F7" s="357" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G7" s="166" t="s">
         <v>18</v>
@@ -33476,7 +33476,7 @@
         <v>330</v>
       </c>
       <c r="F10" s="357" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G10" s="166" t="s">
         <v>18</v>
@@ -33520,7 +33520,7 @@
       <c r="A13" s="140"/>
       <c r="B13" s="142"/>
       <c r="C13" s="358" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D13" s="187" t="s">
         <v>281</v>
@@ -33580,7 +33580,7 @@
         <v>347</v>
       </c>
       <c r="F16" s="357" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G16" s="190" t="s">
         <v>104</v>
@@ -33642,13 +33642,13 @@
       <c r="B20" s="142"/>
       <c r="C20" s="364"/>
       <c r="D20" s="369" t="s">
+        <v>837</v>
+      </c>
+      <c r="E20" s="370" t="s">
         <v>838</v>
       </c>
-      <c r="E20" s="370" t="s">
-        <v>839</v>
-      </c>
       <c r="F20" s="371" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G20" s="372" t="s">
         <v>104</v>
@@ -33701,7 +33701,7 @@
         <v>371</v>
       </c>
       <c r="F23" s="357" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G23" s="166" t="s">
         <v>18</v>
@@ -33718,7 +33718,7 @@
         <v>374</v>
       </c>
       <c r="F24" s="357" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G24" s="166" t="s">
         <v>18</v>
@@ -33752,7 +33752,7 @@
         <v>381</v>
       </c>
       <c r="F26" s="357" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G26" s="166" t="s">
         <v>18</v>
@@ -33786,7 +33786,7 @@
         <v>389</v>
       </c>
       <c r="F28" s="359" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G28" s="178" t="s">
         <v>18</v>
@@ -33805,7 +33805,7 @@
         <v>343</v>
       </c>
       <c r="F29" s="361" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G29" s="188" t="s">
         <v>18</v>
@@ -33822,7 +33822,7 @@
         <v>398</v>
       </c>
       <c r="F30" s="357" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G30" s="166" t="s">
         <v>18</v>
@@ -33839,7 +33839,7 @@
         <v>404</v>
       </c>
       <c r="F31" s="186" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G31" s="198" t="s">
         <v>104</v>
@@ -33858,7 +33858,7 @@
         <v>384</v>
       </c>
       <c r="F32" s="361" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G32" s="188" t="s">
         <v>18</v>
@@ -33869,13 +33869,13 @@
       <c r="B33" s="142"/>
       <c r="C33" s="195"/>
       <c r="D33" s="360" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E33" s="173" t="s">
         <v>407</v>
       </c>
       <c r="F33" s="359" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G33" s="178" t="s">
         <v>18</v>
@@ -33894,7 +33894,7 @@
         <v>376</v>
       </c>
       <c r="F34" s="361" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G34" s="188" t="s">
         <v>18</v>
@@ -33905,13 +33905,13 @@
       <c r="B35" s="142"/>
       <c r="C35" s="195"/>
       <c r="D35" s="360" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E35" s="173" t="s">
         <v>411</v>
       </c>
       <c r="F35" s="359" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G35" s="178" t="s">
         <v>18</v>
@@ -34028,13 +34028,13 @@
       <c r="B42" s="142"/>
       <c r="C42" s="195"/>
       <c r="D42" s="360" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E42" s="173" t="s">
         <v>437</v>
       </c>
       <c r="F42" s="359" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="G42" s="178" t="s">
         <v>18</v>
@@ -34072,7 +34072,7 @@
         <v>430</v>
       </c>
       <c r="F44" s="361" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G44" s="188" t="s">
         <v>18</v>
@@ -34083,13 +34083,13 @@
       <c r="B45" s="142"/>
       <c r="C45" s="195"/>
       <c r="D45" s="360" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E45" s="173" t="s">
         <v>442</v>
       </c>
       <c r="F45" s="359" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G45" s="178" t="s">
         <v>18</v>
@@ -34119,13 +34119,13 @@
       <c r="B47" s="142"/>
       <c r="C47" s="195"/>
       <c r="D47" s="360" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E47" s="173" t="s">
         <v>445</v>
       </c>
       <c r="F47" s="359" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G47" s="178" t="s">
         <v>18</v>
@@ -34144,7 +34144,7 @@
         <v>447</v>
       </c>
       <c r="F48" s="356" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G48" s="226" t="s">
         <v>18</v>
@@ -34163,7 +34163,7 @@
         <v>450</v>
       </c>
       <c r="F49" s="356" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G49" s="229" t="s">
         <v>104</v>
@@ -34201,7 +34201,7 @@
         <v>456</v>
       </c>
       <c r="F51" s="182" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G51" s="188" t="s">
         <v>18</v>
@@ -34218,7 +34218,7 @@
         <v>458</v>
       </c>
       <c r="F52" s="164" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G52" s="166" t="s">
         <v>18</v>
@@ -34235,7 +34235,7 @@
         <v>460</v>
       </c>
       <c r="F53" s="357" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G53" s="166" t="s">
         <v>18</v>
@@ -34252,7 +34252,7 @@
         <v>462</v>
       </c>
       <c r="F54" s="357" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G54" s="166" t="s">
         <v>18</v>
@@ -34269,7 +34269,7 @@
         <v>464</v>
       </c>
       <c r="F55" s="357" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G55" s="166" t="s">
         <v>18</v>
@@ -34305,7 +34305,7 @@
         <v>471</v>
       </c>
       <c r="F57" s="361" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G57" s="235" t="s">
         <v>104</v>
@@ -34322,7 +34322,7 @@
         <v>477</v>
       </c>
       <c r="F58" s="357" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G58" s="190" t="s">
         <v>104</v>
@@ -34333,13 +34333,13 @@
       <c r="B59" s="140"/>
       <c r="C59" s="231"/>
       <c r="D59" s="237" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E59" s="161" t="s">
         <v>480</v>
       </c>
       <c r="F59" s="357" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="G59" s="190" t="s">
         <v>104</v>
@@ -34367,13 +34367,13 @@
       <c r="B61" s="140"/>
       <c r="C61" s="231"/>
       <c r="D61" s="237" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E61" s="161" t="s">
         <v>495</v>
       </c>
       <c r="F61" s="357" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G61" s="190" t="s">
         <v>104</v>
@@ -34420,13 +34420,13 @@
       <c r="B64" s="140"/>
       <c r="C64" s="244"/>
       <c r="D64" s="211" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E64" s="173" t="s">
         <v>533</v>
       </c>
       <c r="F64" s="359" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G64" s="198" t="s">
         <v>104</v>
@@ -34445,7 +34445,7 @@
         <v>488</v>
       </c>
       <c r="F65" s="361" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G65" s="235" t="s">
         <v>104</v>
@@ -34456,13 +34456,13 @@
       <c r="B66" s="140"/>
       <c r="C66" s="244"/>
       <c r="D66" s="211" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E66" s="173" t="s">
         <v>544</v>
       </c>
       <c r="F66" s="359" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G66" s="198" t="s">
         <v>104</v>
@@ -34475,13 +34475,13 @@
         <v>545</v>
       </c>
       <c r="D67" s="233" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E67" s="181" t="s">
         <v>546</v>
       </c>
       <c r="F67" s="361" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G67" s="235" t="s">
         <v>104</v>
@@ -34492,13 +34492,13 @@
       <c r="B68" s="140"/>
       <c r="C68" s="244"/>
       <c r="D68" s="211" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E68" s="173" t="s">
         <v>547</v>
       </c>
       <c r="F68" s="359" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G68" s="198" t="s">
         <v>104</v>
@@ -34881,55 +34881,55 @@
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="C29" s="296"/>
       <c r="D29" s="306" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E29" s="337" t="s">
+        <v>777</v>
+      </c>
+      <c r="F29" s="307" t="s">
         <v>778</v>
-      </c>
-      <c r="F29" s="307" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="14">
       <c r="C30" s="296"/>
       <c r="D30" s="302"/>
       <c r="E30" s="339" t="s">
+        <v>779</v>
+      </c>
+      <c r="F30" s="340" t="s">
         <v>780</v>
-      </c>
-      <c r="F30" s="340" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14">
       <c r="C31" s="296"/>
       <c r="D31" s="302"/>
       <c r="E31" s="337" t="s">
+        <v>781</v>
+      </c>
+      <c r="F31" s="340" t="s">
         <v>782</v>
-      </c>
-      <c r="F31" s="340" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
       <c r="C32" s="296"/>
       <c r="D32" s="302"/>
       <c r="E32" s="337" t="s">
+        <v>783</v>
+      </c>
+      <c r="F32" s="308" t="s">
         <v>784</v>
-      </c>
-      <c r="F32" s="308" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="33" spans="3:6" ht="15.75" customHeight="1">
       <c r="C33" s="296"/>
       <c r="D33" s="306" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E33" s="342" t="s">
         <v>632</v>
       </c>
       <c r="F33" s="303" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="34" spans="3:6" ht="15.75" customHeight="1">
@@ -34945,7 +34945,7 @@
     <row r="35" spans="3:6" ht="15.75" customHeight="1">
       <c r="C35" s="296"/>
       <c r="D35" s="306" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E35" s="343" t="s">
         <v>625</v>
@@ -34971,7 +34971,7 @@
         <v>627</v>
       </c>
       <c r="F37" s="307" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="38" spans="3:6" ht="14">
@@ -34981,7 +34981,7 @@
         <v>629</v>
       </c>
       <c r="F38" s="346" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="39" spans="3:6" ht="15.75" customHeight="1">
@@ -34991,7 +34991,7 @@
         <v>630</v>
       </c>
       <c r="F39" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="40" spans="3:6" ht="15.75" customHeight="1">
@@ -35001,7 +35001,7 @@
         <v>631</v>
       </c>
       <c r="F40" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="41" spans="3:6" ht="15.75" customHeight="1">
@@ -35011,23 +35011,23 @@
         <v>617</v>
       </c>
       <c r="F41" s="354" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="42" spans="3:6" ht="14">
       <c r="C42" s="296"/>
       <c r="D42" s="332"/>
       <c r="E42" s="345" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F42" s="352" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="43" spans="3:6" ht="15.75" customHeight="1">
       <c r="C43" s="296"/>
       <c r="D43" s="306" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E43" s="343" t="s">
         <v>625</v>
@@ -35053,7 +35053,7 @@
         <v>627</v>
       </c>
       <c r="F45" s="307" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="46" spans="3:6" ht="14">
@@ -35063,7 +35063,7 @@
         <v>629</v>
       </c>
       <c r="F46" s="346" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="47" spans="3:6" ht="15.75" customHeight="1">
@@ -35073,7 +35073,7 @@
         <v>630</v>
       </c>
       <c r="F47" s="310" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="48" spans="3:6" ht="15.75" customHeight="1">
@@ -35083,7 +35083,7 @@
         <v>631</v>
       </c>
       <c r="F48" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="49" spans="3:6" ht="15.75" customHeight="1">
@@ -35093,29 +35093,29 @@
         <v>617</v>
       </c>
       <c r="F49" s="354" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="50" spans="3:6" ht="14">
       <c r="C50" s="296"/>
       <c r="D50" s="332"/>
       <c r="E50" s="345" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F50" s="352" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="51" spans="3:6" ht="15.75" customHeight="1">
       <c r="C51" s="296"/>
       <c r="D51" s="306" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E51" s="342" t="s">
         <v>632</v>
       </c>
       <c r="F51" s="303" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="52" spans="3:6" ht="15.75" customHeight="1">
@@ -35131,49 +35131,49 @@
     <row r="53" spans="3:6" ht="15">
       <c r="C53" s="296"/>
       <c r="D53" s="347" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E53" s="345" t="s">
         <v>608</v>
       </c>
       <c r="F53" s="303" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="54" spans="3:6" ht="15">
       <c r="C54" s="296"/>
       <c r="D54" s="341" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E54" s="345" t="s">
         <v>608</v>
       </c>
       <c r="F54" s="303" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="55" spans="3:6" ht="15.75" customHeight="1">
       <c r="C55" s="296"/>
       <c r="D55" s="348" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E55" s="344" t="s">
         <v>685</v>
       </c>
       <c r="F55" s="333" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="56" spans="3:6" ht="15.75" customHeight="1">
       <c r="C56" s="300"/>
       <c r="D56" s="349" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E56" s="334" t="s">
         <v>644</v>
       </c>
       <c r="F56" s="335" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="57" spans="3:6" ht="15.75" customHeight="1">
@@ -35183,76 +35183,76 @@
         <v>687</v>
       </c>
       <c r="F57" s="350" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="58" spans="3:6" ht="15.75" customHeight="1">
       <c r="C58" s="301"/>
       <c r="D58" s="351" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E58" s="334" t="s">
         <v>687</v>
       </c>
       <c r="F58" s="350" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="59" spans="3:6" ht="15.75" customHeight="1">
       <c r="C59" s="301"/>
       <c r="D59" s="306" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E59" s="337" t="s">
+        <v>777</v>
+      </c>
+      <c r="F59" s="307" t="s">
         <v>778</v>
-      </c>
-      <c r="F59" s="307" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="60" spans="3:6" ht="14">
       <c r="C60" s="301"/>
       <c r="D60" s="302"/>
       <c r="E60" s="339" t="s">
+        <v>779</v>
+      </c>
+      <c r="F60" s="340" t="s">
         <v>780</v>
-      </c>
-      <c r="F60" s="340" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="61" spans="3:6" ht="14">
       <c r="C61" s="301"/>
       <c r="D61" s="302"/>
       <c r="E61" s="353" t="s">
+        <v>781</v>
+      </c>
+      <c r="F61" s="355" t="s">
         <v>782</v>
-      </c>
-      <c r="F61" s="355" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="62" spans="3:6" ht="15.75" customHeight="1">
       <c r="C62" s="301"/>
       <c r="D62" s="302"/>
       <c r="E62" s="337" t="s">
+        <v>783</v>
+      </c>
+      <c r="F62" s="308" t="s">
         <v>784</v>
-      </c>
-      <c r="F62" s="308" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="63" spans="3:6" ht="15.75" customHeight="1">
       <c r="C63" s="301"/>
       <c r="D63" s="304"/>
       <c r="E63" s="337" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="F63" s="308" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="64" spans="3:6" ht="15.75" customHeight="1">
       <c r="D64" s="306" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E64" s="343" t="s">
         <v>625</v>
@@ -35276,7 +35276,7 @@
         <v>627</v>
       </c>
       <c r="F66" s="307" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="67" spans="3:6" ht="15.75" customHeight="1">
@@ -35285,7 +35285,7 @@
         <v>629</v>
       </c>
       <c r="F67" s="346" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="68" spans="3:6" ht="15.75" customHeight="1">
@@ -35294,7 +35294,7 @@
         <v>630</v>
       </c>
       <c r="F68" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="69" spans="3:6" ht="15.75" customHeight="1">
@@ -35303,21 +35303,21 @@
         <v>631</v>
       </c>
       <c r="F69" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="70" spans="3:6" ht="14">
       <c r="D70" s="332"/>
       <c r="E70" s="345" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F70" s="352" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="71" spans="3:6" ht="15.75" customHeight="1">
       <c r="D71" s="306" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E71" s="343" t="s">
         <v>625</v>
@@ -35341,7 +35341,7 @@
         <v>627</v>
       </c>
       <c r="F73" s="307" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="74" spans="3:6" ht="15.75" customHeight="1">
@@ -35350,7 +35350,7 @@
         <v>629</v>
       </c>
       <c r="F74" s="346" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="75" spans="3:6" ht="15.75" customHeight="1">
@@ -35359,7 +35359,7 @@
         <v>630</v>
       </c>
       <c r="F75" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="76" spans="3:6" ht="15.75" customHeight="1">
@@ -35368,21 +35368,21 @@
         <v>631</v>
       </c>
       <c r="F76" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="77" spans="3:6" ht="14">
       <c r="D77" s="332"/>
       <c r="E77" s="345" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F77" s="352" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="80" spans="3:6" ht="15.75" customHeight="1">
       <c r="C80" s="373" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D80" s="297"/>
       <c r="E80" s="297"/>
@@ -35394,10 +35394,10 @@
         <v>602</v>
       </c>
       <c r="E81" s="374" t="s">
+        <v>855</v>
+      </c>
+      <c r="F81" s="375" t="s">
         <v>856</v>
-      </c>
-      <c r="F81" s="375" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="82" spans="3:6" ht="15.75" customHeight="1">
@@ -35451,51 +35451,51 @@
     </row>
     <row r="87" spans="3:6" ht="15.75" customHeight="1">
       <c r="D87" s="306" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E87" s="337" t="s">
+        <v>777</v>
+      </c>
+      <c r="F87" s="307" t="s">
         <v>778</v>
-      </c>
-      <c r="F87" s="307" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="88" spans="3:6" ht="15.75" customHeight="1">
       <c r="D88" s="302"/>
       <c r="E88" s="339" t="s">
+        <v>779</v>
+      </c>
+      <c r="F88" s="340" t="s">
         <v>780</v>
-      </c>
-      <c r="F88" s="340" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="89" spans="3:6" ht="15.75" customHeight="1">
       <c r="D89" s="302"/>
       <c r="E89" s="337" t="s">
+        <v>781</v>
+      </c>
+      <c r="F89" s="340" t="s">
         <v>782</v>
-      </c>
-      <c r="F89" s="340" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="90" spans="3:6" ht="15.75" customHeight="1">
       <c r="D90" s="302"/>
       <c r="E90" s="337" t="s">
+        <v>783</v>
+      </c>
+      <c r="F90" s="308" t="s">
         <v>784</v>
-      </c>
-      <c r="F90" s="308" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="91" spans="3:6" ht="15.75" customHeight="1">
       <c r="D91" s="306" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E91" s="342" t="s">
         <v>632</v>
       </c>
       <c r="F91" s="303" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="92" spans="3:6" ht="15.75" customHeight="1">
@@ -35509,7 +35509,7 @@
     </row>
     <row r="93" spans="3:6" ht="15.75" customHeight="1">
       <c r="D93" s="306" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E93" s="343" t="s">
         <v>625</v>
@@ -35533,7 +35533,7 @@
         <v>627</v>
       </c>
       <c r="F95" s="307" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="96" spans="3:6" ht="15.75" customHeight="1">
@@ -35542,7 +35542,7 @@
         <v>629</v>
       </c>
       <c r="F96" s="346" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="97" spans="4:6" ht="15.75" customHeight="1">
@@ -35551,7 +35551,7 @@
         <v>630</v>
       </c>
       <c r="F97" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="98" spans="4:6" ht="15.75" customHeight="1">
@@ -35560,7 +35560,7 @@
         <v>631</v>
       </c>
       <c r="F98" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="99" spans="4:6" ht="15.75" customHeight="1">
@@ -35569,21 +35569,21 @@
         <v>617</v>
       </c>
       <c r="F99" s="354" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="100" spans="4:6" ht="15.75" customHeight="1">
       <c r="D100" s="332"/>
       <c r="E100" s="345" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F100" s="352" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="101" spans="4:6" ht="15.75" customHeight="1">
       <c r="D101" s="306" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E101" s="343" t="s">
         <v>625</v>
@@ -35607,7 +35607,7 @@
         <v>627</v>
       </c>
       <c r="F103" s="307" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="104" spans="4:6" ht="15.75" customHeight="1">
@@ -35616,7 +35616,7 @@
         <v>629</v>
       </c>
       <c r="F104" s="346" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="105" spans="4:6" ht="15.75" customHeight="1">
@@ -35625,7 +35625,7 @@
         <v>630</v>
       </c>
       <c r="F105" s="310" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="106" spans="4:6" ht="15.75" customHeight="1">
@@ -35634,7 +35634,7 @@
         <v>631</v>
       </c>
       <c r="F106" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="107" spans="4:6" ht="15.75" customHeight="1">
@@ -35643,27 +35643,27 @@
         <v>617</v>
       </c>
       <c r="F107" s="354" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="108" spans="4:6" ht="15.75" customHeight="1">
       <c r="D108" s="332"/>
       <c r="E108" s="345" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F108" s="352" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="109" spans="4:6" ht="15.75" customHeight="1">
       <c r="D109" s="306" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E109" s="342" t="s">
         <v>632</v>
       </c>
       <c r="F109" s="303" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="110" spans="4:6" ht="15.75" customHeight="1">
@@ -35677,46 +35677,46 @@
     </row>
     <row r="111" spans="4:6" ht="15.75" customHeight="1">
       <c r="D111" s="347" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E111" s="345" t="s">
         <v>608</v>
       </c>
       <c r="F111" s="303" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="112" spans="4:6" ht="15.75" customHeight="1">
       <c r="D112" s="341" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E112" s="345" t="s">
         <v>608</v>
       </c>
       <c r="F112" s="303" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="113" spans="4:6" ht="15.75" customHeight="1">
       <c r="D113" s="348" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E113" s="344" t="s">
         <v>685</v>
       </c>
       <c r="F113" s="333" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="114" spans="4:6" ht="15.75" customHeight="1">
       <c r="D114" s="349" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E114" s="334" t="s">
         <v>644</v>
       </c>
       <c r="F114" s="335" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="115" spans="4:6" ht="15.75" customHeight="1">
@@ -35725,70 +35725,70 @@
         <v>687</v>
       </c>
       <c r="F115" s="350" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="116" spans="4:6" ht="15.75" customHeight="1">
       <c r="D116" s="351" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E116" s="334" t="s">
         <v>687</v>
       </c>
       <c r="F116" s="350" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="117" spans="4:6" ht="15.75" customHeight="1">
       <c r="D117" s="306" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E117" s="337" t="s">
+        <v>777</v>
+      </c>
+      <c r="F117" s="307" t="s">
         <v>778</v>
-      </c>
-      <c r="F117" s="307" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="118" spans="4:6" ht="15.75" customHeight="1">
       <c r="D118" s="302"/>
       <c r="E118" s="339" t="s">
+        <v>779</v>
+      </c>
+      <c r="F118" s="340" t="s">
         <v>780</v>
-      </c>
-      <c r="F118" s="340" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="119" spans="4:6" ht="15.75" customHeight="1">
       <c r="D119" s="302"/>
       <c r="E119" s="353" t="s">
+        <v>781</v>
+      </c>
+      <c r="F119" s="355" t="s">
         <v>782</v>
-      </c>
-      <c r="F119" s="355" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="120" spans="4:6" ht="15.75" customHeight="1">
       <c r="D120" s="302"/>
       <c r="E120" s="337" t="s">
+        <v>783</v>
+      </c>
+      <c r="F120" s="308" t="s">
         <v>784</v>
-      </c>
-      <c r="F120" s="308" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="121" spans="4:6" ht="15.75" customHeight="1">
       <c r="D121" s="304"/>
       <c r="E121" s="337" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="F121" s="308" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="122" spans="4:6" ht="15.75" customHeight="1">
       <c r="D122" s="306" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E122" s="343" t="s">
         <v>625</v>
@@ -35812,7 +35812,7 @@
         <v>627</v>
       </c>
       <c r="F124" s="307" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="125" spans="4:6" ht="15.75" customHeight="1">
@@ -35821,7 +35821,7 @@
         <v>629</v>
       </c>
       <c r="F125" s="346" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="126" spans="4:6" ht="15.75" customHeight="1">
@@ -35830,7 +35830,7 @@
         <v>630</v>
       </c>
       <c r="F126" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="127" spans="4:6" ht="15.75" customHeight="1">
@@ -35839,21 +35839,21 @@
         <v>631</v>
       </c>
       <c r="F127" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="128" spans="4:6" ht="15.75" customHeight="1">
       <c r="D128" s="332"/>
       <c r="E128" s="345" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F128" s="352" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="129" spans="4:6" ht="15.75" customHeight="1">
       <c r="D129" s="306" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E129" s="343" t="s">
         <v>625</v>
@@ -35877,7 +35877,7 @@
         <v>627</v>
       </c>
       <c r="F131" s="307" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="132" spans="4:6" ht="15.75" customHeight="1">
@@ -35886,7 +35886,7 @@
         <v>629</v>
       </c>
       <c r="F132" s="346" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="133" spans="4:6" ht="15.75" customHeight="1">
@@ -35895,7 +35895,7 @@
         <v>630</v>
       </c>
       <c r="F133" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="134" spans="4:6" ht="15.75" customHeight="1">
@@ -35904,16 +35904,16 @@
         <v>631</v>
       </c>
       <c r="F134" s="307" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="135" spans="4:6" ht="15.75" customHeight="1">
       <c r="D135" s="332"/>
       <c r="E135" s="345" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F135" s="352" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
   </sheetData>

--- a/docs/大島 佑斗さん_新模擬案件_Bookshelf_要件シート.xlsx
+++ b/docs/大島 佑斗さん_新模擬案件_Bookshelf_要件シート.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE412B30-767D-F841-9049-F4B63EC2BE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FD6AD0-F9EB-2644-9294-B99CD7CADBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="シート1 ターム内容" sheetId="1" r:id="rId1"/>
@@ -3145,33 +3145,6 @@
     <phoneticPr fontId="73"/>
   </si>
   <si>
-    <r>
-      <t>user_review(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>いいね</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="73"/>
-  </si>
-  <si>
     <t>ユーザモデルではlikedReviews()</t>
     <phoneticPr fontId="73"/>
   </si>
@@ -12861,6 +12834,33 @@
   </si>
   <si>
     <t>password / confirm</t>
+    <phoneticPr fontId="73"/>
+  </si>
+  <si>
+    <r>
+      <t>review_user(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>いいね</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
     <phoneticPr fontId="73"/>
   </si>
 </sst>
@@ -14521,7 +14521,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11"/>
   </cellStyleXfs>
-  <cellXfs count="470">
+  <cellXfs count="459">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -15574,14 +15574,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -15606,9 +15598,6 @@
     </xf>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -15637,31 +15626,15 @@
     <xf numFmtId="0" fontId="111" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -17579,7 +17552,7 @@
       <c r="I6" s="254"/>
       <c r="J6" s="255"/>
       <c r="K6" s="256" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="13">
@@ -17604,7 +17577,7 @@
         <v>561</v>
       </c>
       <c r="K7" s="262" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="13">
@@ -17625,7 +17598,7 @@
       <c r="I8" s="258"/>
       <c r="J8" s="261"/>
       <c r="K8" s="262" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="13">
@@ -17648,7 +17621,7 @@
         <v>618</v>
       </c>
       <c r="K9" s="262" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="13">
@@ -17669,7 +17642,7 @@
         <v>570</v>
       </c>
       <c r="K10" s="262" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="13">
@@ -17690,7 +17663,7 @@
       <c r="I11" s="258"/>
       <c r="J11" s="261"/>
       <c r="K11" s="262" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="13">
@@ -17702,7 +17675,7 @@
         <v>572</v>
       </c>
       <c r="F12" s="258" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G12" s="258"/>
       <c r="H12" s="258"/>
@@ -17711,7 +17684,7 @@
         <v>573</v>
       </c>
       <c r="K12" s="262" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="13">
@@ -17723,7 +17696,7 @@
         <v>577</v>
       </c>
       <c r="F13" s="258" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G13" s="258"/>
       <c r="H13" s="258"/>
@@ -17732,7 +17705,7 @@
         <v>579</v>
       </c>
       <c r="K13" s="262" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="13">
@@ -17753,7 +17726,7 @@
         <v>579</v>
       </c>
       <c r="K14" s="262" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="13">
@@ -17770,7 +17743,7 @@
         <v>581</v>
       </c>
       <c r="K15" s="262" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13">
@@ -17787,7 +17760,7 @@
       <c r="I16" s="273"/>
       <c r="J16" s="274"/>
       <c r="K16" s="262" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="14">
@@ -17795,7 +17768,7 @@
       <c r="B17" s="285"/>
       <c r="C17" s="252"/>
       <c r="D17" s="253" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E17" s="254"/>
       <c r="F17" s="254"/>
@@ -17804,7 +17777,7 @@
       <c r="I17" s="254"/>
       <c r="J17" s="255"/>
       <c r="K17" s="287" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="13">
@@ -17827,7 +17800,7 @@
       <c r="I18" s="258"/>
       <c r="J18" s="261"/>
       <c r="K18" s="287" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="13">
@@ -17836,7 +17809,7 @@
       <c r="C19" s="257"/>
       <c r="D19" s="284"/>
       <c r="E19" s="258" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F19" s="258" t="s">
         <v>617</v>
@@ -17848,7 +17821,7 @@
       <c r="I19" s="258"/>
       <c r="J19" s="261"/>
       <c r="K19" s="287" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="13">
@@ -17857,10 +17830,10 @@
       <c r="C20" s="257"/>
       <c r="D20" s="284"/>
       <c r="E20" s="258" t="s">
+        <v>659</v>
+      </c>
+      <c r="F20" s="258" t="s">
         <v>660</v>
-      </c>
-      <c r="F20" s="258" t="s">
-        <v>661</v>
       </c>
       <c r="G20" s="258"/>
       <c r="H20" s="258" t="s">
@@ -17868,10 +17841,10 @@
       </c>
       <c r="I20" s="258"/>
       <c r="J20" s="261" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K20" s="287" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="14">
@@ -17879,7 +17852,7 @@
       <c r="B21" s="285"/>
       <c r="C21" s="252"/>
       <c r="D21" s="253" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E21" s="254"/>
       <c r="F21" s="254"/>
@@ -17888,7 +17861,7 @@
       <c r="I21" s="254"/>
       <c r="J21" s="255"/>
       <c r="K21" s="287" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="13">
@@ -17900,7 +17873,7 @@
         <v>557</v>
       </c>
       <c r="F22" s="258" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G22" s="258" t="s">
         <v>559</v>
@@ -17913,7 +17886,7 @@
         <v>561</v>
       </c>
       <c r="K22" s="287" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="13">
@@ -17922,10 +17895,10 @@
       <c r="C23" s="257"/>
       <c r="D23" s="284"/>
       <c r="E23" s="258" t="s">
+        <v>663</v>
+      </c>
+      <c r="F23" s="258" t="s">
         <v>664</v>
-      </c>
-      <c r="F23" s="258" t="s">
-        <v>665</v>
       </c>
       <c r="G23" s="258"/>
       <c r="H23" s="258" t="s">
@@ -17933,10 +17906,10 @@
       </c>
       <c r="I23" s="258"/>
       <c r="J23" s="261" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="K23" s="287" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="13">
@@ -17945,7 +17918,7 @@
       <c r="C24" s="257"/>
       <c r="D24" s="284"/>
       <c r="E24" s="258" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F24" s="258" t="s">
         <v>617</v>
@@ -17956,10 +17929,10 @@
       </c>
       <c r="I24" s="258"/>
       <c r="J24" s="261" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="K24" s="287" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="13">
@@ -17980,7 +17953,7 @@
       <c r="I25" s="258"/>
       <c r="J25" s="261"/>
       <c r="K25" s="287" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="13">
@@ -17989,10 +17962,10 @@
       <c r="C26" s="257"/>
       <c r="D26" s="13"/>
       <c r="E26" s="258" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F26" s="258" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G26" s="258"/>
       <c r="H26" s="258" t="s">
@@ -18003,7 +17976,7 @@
         <v>618</v>
       </c>
       <c r="K26" s="287" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="13">
@@ -18012,17 +17985,17 @@
       <c r="C27" s="257"/>
       <c r="D27" s="13"/>
       <c r="E27" s="258" t="s">
+        <v>666</v>
+      </c>
+      <c r="F27" s="258" t="s">
         <v>667</v>
-      </c>
-      <c r="F27" s="258" t="s">
-        <v>668</v>
       </c>
       <c r="G27" s="258"/>
       <c r="H27" s="258"/>
       <c r="I27" s="258"/>
       <c r="J27" s="261"/>
       <c r="K27" s="287" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="13">
@@ -18031,17 +18004,17 @@
       <c r="C28" s="257"/>
       <c r="D28" s="13"/>
       <c r="E28" s="258" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F28" s="258" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G28" s="258"/>
       <c r="H28" s="258"/>
       <c r="I28" s="258"/>
       <c r="J28" s="261"/>
       <c r="K28" s="287" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="13">
@@ -18050,17 +18023,17 @@
       <c r="C29" s="316"/>
       <c r="D29" s="317"/>
       <c r="E29" s="258" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F29" s="258" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G29" s="258"/>
       <c r="H29" s="258"/>
       <c r="I29" s="258"/>
       <c r="J29" s="261"/>
       <c r="K29" s="320" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="13">
@@ -18072,7 +18045,7 @@
         <v>577</v>
       </c>
       <c r="F30" s="258" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G30" s="258"/>
       <c r="H30" s="258"/>
@@ -18081,7 +18054,7 @@
         <v>579</v>
       </c>
       <c r="K30" s="320" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="13">
@@ -18102,7 +18075,7 @@
         <v>579</v>
       </c>
       <c r="K31" s="320" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="14">
@@ -18110,7 +18083,7 @@
       <c r="B32" s="285"/>
       <c r="C32" s="252"/>
       <c r="D32" s="253" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E32" s="254"/>
       <c r="F32" s="254"/>
@@ -18119,7 +18092,7 @@
       <c r="I32" s="254"/>
       <c r="J32" s="255"/>
       <c r="K32" s="287" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="13">
@@ -18144,7 +18117,7 @@
         <v>561</v>
       </c>
       <c r="K33" s="287" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="13">
@@ -18153,7 +18126,7 @@
       <c r="C34" s="257"/>
       <c r="D34" s="284"/>
       <c r="E34" s="258" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F34" s="258" t="s">
         <v>617</v>
@@ -18167,7 +18140,7 @@
         <v>618</v>
       </c>
       <c r="K34" s="287" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="13">
@@ -18176,10 +18149,10 @@
       <c r="C35" s="257"/>
       <c r="D35" s="284"/>
       <c r="E35" s="258" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F35" s="258" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G35" s="258"/>
       <c r="H35" s="258" t="s">
@@ -18188,7 +18161,7 @@
       <c r="I35" s="258"/>
       <c r="J35" s="261"/>
       <c r="K35" s="287" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="13">
@@ -18197,10 +18170,10 @@
       <c r="C36" s="257"/>
       <c r="D36" s="284"/>
       <c r="E36" s="258" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F36" s="258" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G36" s="258"/>
       <c r="H36" s="258" t="s">
@@ -18209,7 +18182,7 @@
       <c r="I36" s="258"/>
       <c r="J36" s="261"/>
       <c r="K36" s="287" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="13">
@@ -18218,10 +18191,10 @@
       <c r="C37" s="257"/>
       <c r="D37" s="284"/>
       <c r="E37" s="258" t="s">
+        <v>674</v>
+      </c>
+      <c r="F37" s="258" t="s">
         <v>675</v>
-      </c>
-      <c r="F37" s="258" t="s">
-        <v>676</v>
       </c>
       <c r="G37" s="258"/>
       <c r="H37" s="258" t="s">
@@ -18230,7 +18203,7 @@
       <c r="I37" s="258"/>
       <c r="J37" s="261"/>
       <c r="K37" s="287" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="13">
@@ -18239,10 +18212,10 @@
       <c r="C38" s="257"/>
       <c r="D38" s="13"/>
       <c r="E38" s="258" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F38" s="258" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G38" s="258"/>
       <c r="H38" s="258" t="s">
@@ -18251,7 +18224,7 @@
       <c r="I38" s="258"/>
       <c r="J38" s="261"/>
       <c r="K38" s="320" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="13">
@@ -18260,10 +18233,10 @@
       <c r="C39" s="286"/>
       <c r="D39" s="288"/>
       <c r="E39" s="258" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F39" s="258" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G39" s="258"/>
       <c r="H39" s="258" t="s">
@@ -18271,10 +18244,10 @@
       </c>
       <c r="I39" s="258"/>
       <c r="J39" s="261" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="K39" s="320" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="13">
@@ -18291,7 +18264,7 @@
       <c r="I40" s="254"/>
       <c r="J40" s="255"/>
       <c r="K40" s="256" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="13">
@@ -18316,7 +18289,7 @@
         <v>561</v>
       </c>
       <c r="K41" s="262" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="14">
@@ -18341,7 +18314,7 @@
         <v>620</v>
       </c>
       <c r="K42" s="262" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="13">
@@ -18362,7 +18335,7 @@
       <c r="I43" s="258"/>
       <c r="J43" s="261"/>
       <c r="K43" s="262" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="13">
@@ -18383,7 +18356,7 @@
       <c r="I44" s="258"/>
       <c r="J44" s="261"/>
       <c r="K44" s="262" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="13">
@@ -18406,7 +18379,7 @@
         <v>618</v>
       </c>
       <c r="K45" s="262" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="14">
@@ -18426,10 +18399,10 @@
       </c>
       <c r="I46" s="258"/>
       <c r="J46" s="319" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="K46" s="262" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="13">
@@ -18441,14 +18414,14 @@
         <v>626</v>
       </c>
       <c r="F47" s="258" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G47" s="258"/>
       <c r="H47" s="258"/>
       <c r="I47" s="258"/>
       <c r="J47" s="261"/>
       <c r="K47" s="262" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="13">
@@ -18467,7 +18440,7 @@
       <c r="I48" s="258"/>
       <c r="J48" s="261"/>
       <c r="K48" s="262" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="13">
@@ -18488,7 +18461,7 @@
         <v>579</v>
       </c>
       <c r="K49" s="262" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="13">
@@ -18509,7 +18482,7 @@
         <v>579</v>
       </c>
       <c r="K50" s="262" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="13">
@@ -18526,7 +18499,7 @@
       <c r="I51" s="254"/>
       <c r="J51" s="255"/>
       <c r="K51" s="256" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="13">
@@ -18551,7 +18524,7 @@
         <v>561</v>
       </c>
       <c r="K52" s="262" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="13">
@@ -18574,7 +18547,7 @@
         <v>618</v>
       </c>
       <c r="K53" s="262" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="13">
@@ -18595,7 +18568,7 @@
         <v>579</v>
       </c>
       <c r="K54" s="262" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="13">
@@ -18616,7 +18589,7 @@
         <v>579</v>
       </c>
       <c r="K55" s="262" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="13">
@@ -18624,7 +18597,7 @@
       <c r="B56" s="285"/>
       <c r="C56" s="252"/>
       <c r="D56" s="253" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E56" s="254"/>
       <c r="F56" s="254"/>
@@ -18633,7 +18606,7 @@
       <c r="I56" s="254"/>
       <c r="J56" s="255"/>
       <c r="K56" s="287" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="13">
@@ -18658,7 +18631,7 @@
         <v>561</v>
       </c>
       <c r="K57" s="287" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="14">
@@ -18683,7 +18656,7 @@
         <v>637</v>
       </c>
       <c r="K58" s="287" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="14">
@@ -18692,7 +18665,7 @@
       <c r="C59" s="257"/>
       <c r="D59" s="284"/>
       <c r="E59" s="258" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F59" s="258" t="s">
         <v>558</v>
@@ -18702,13 +18675,13 @@
         <v>559</v>
       </c>
       <c r="I59" s="258" t="s">
+        <v>650</v>
+      </c>
+      <c r="J59" s="313" t="s">
         <v>651</v>
       </c>
-      <c r="J59" s="313" t="s">
-        <v>652</v>
-      </c>
       <c r="K59" s="287" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="13">
@@ -18729,7 +18702,7 @@
         <v>579</v>
       </c>
       <c r="K60" s="287" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="13">
@@ -18750,7 +18723,7 @@
         <v>579</v>
       </c>
       <c r="K61" s="320" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="14">
@@ -18766,10 +18739,10 @@
       <c r="H62" s="258"/>
       <c r="I62" s="258"/>
       <c r="J62" s="261" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K62" s="287" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="13">
@@ -18786,7 +18759,7 @@
       <c r="I63" s="254"/>
       <c r="J63" s="255"/>
       <c r="K63" s="256" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="13">
@@ -18811,7 +18784,7 @@
         <v>561</v>
       </c>
       <c r="K64" s="262" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="14">
@@ -18836,7 +18809,7 @@
         <v>637</v>
       </c>
       <c r="K65" s="262" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="14">
@@ -18861,7 +18834,7 @@
         <v>631</v>
       </c>
       <c r="K66" s="262" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="14">
@@ -18884,7 +18857,7 @@
         <v>634</v>
       </c>
       <c r="K67" s="262" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="13">
@@ -18896,7 +18869,7 @@
         <v>608</v>
       </c>
       <c r="F68" s="258" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="G68" s="281"/>
       <c r="H68" s="258" t="s">
@@ -18905,7 +18878,7 @@
       <c r="I68" s="281"/>
       <c r="J68" s="283"/>
       <c r="K68" s="262" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="13">
@@ -18914,7 +18887,7 @@
       <c r="C69" s="257"/>
       <c r="D69" s="13"/>
       <c r="E69" s="258" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F69" s="258" t="s">
         <v>569</v>
@@ -18926,7 +18899,7 @@
         <v>579</v>
       </c>
       <c r="K69" s="262" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="13">
@@ -18935,7 +18908,7 @@
       <c r="C70" s="257"/>
       <c r="D70" s="13"/>
       <c r="E70" s="258" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F70" s="258" t="s">
         <v>569</v>
@@ -18964,7 +18937,7 @@
         <v>636</v>
       </c>
       <c r="K71" s="262" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="13">
@@ -18989,7 +18962,7 @@
         <v>561</v>
       </c>
       <c r="K72" s="262" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="13">
@@ -19014,7 +18987,7 @@
         <v>638</v>
       </c>
       <c r="K73" s="262" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="14">
@@ -19039,7 +19012,7 @@
         <v>635</v>
       </c>
       <c r="K74" s="262" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="13">
@@ -19060,7 +19033,7 @@
         <v>579</v>
       </c>
       <c r="K75" s="262" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="13">
@@ -19081,7 +19054,7 @@
         <v>579</v>
       </c>
       <c r="K76" s="262" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="14">
@@ -19099,7 +19072,7 @@
         <v>641</v>
       </c>
       <c r="K77" s="262" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="14">
@@ -19107,7 +19080,7 @@
       <c r="B78" s="285"/>
       <c r="C78" s="252"/>
       <c r="D78" s="253" t="s">
-        <v>646</v>
+        <v>1129</v>
       </c>
       <c r="E78" s="254"/>
       <c r="F78" s="254"/>
@@ -19115,10 +19088,10 @@
       <c r="H78" s="254"/>
       <c r="I78" s="254"/>
       <c r="J78" s="314" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="K78" s="287" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="13">
@@ -19143,7 +19116,7 @@
         <v>561</v>
       </c>
       <c r="K79" s="287" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="14">
@@ -19165,7 +19138,7 @@
         <v>644</v>
       </c>
       <c r="J80" s="313" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K80" s="287"/>
     </row>
@@ -19191,7 +19164,7 @@
         <v>643</v>
       </c>
       <c r="K81" s="287" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="13">
@@ -19212,7 +19185,7 @@
         <v>579</v>
       </c>
       <c r="K82" s="287" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="13">
@@ -19233,7 +19206,7 @@
         <v>579</v>
       </c>
       <c r="K83" s="287" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="14">
@@ -19248,10 +19221,10 @@
       <c r="H84" s="258"/>
       <c r="I84" s="258"/>
       <c r="J84" s="261" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="K84" s="287" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="13">
@@ -19268,7 +19241,7 @@
       <c r="I85" s="322"/>
       <c r="J85" s="323"/>
       <c r="K85" s="287" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="13">
@@ -19293,7 +19266,7 @@
         <v>561</v>
       </c>
       <c r="K86" s="287" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="14">
@@ -19315,10 +19288,10 @@
         <v>619</v>
       </c>
       <c r="J87" s="318" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="K87" s="287" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="13">
@@ -19340,10 +19313,10 @@
         <v>632</v>
       </c>
       <c r="J88" s="311" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K88" s="287" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="13">
@@ -19352,7 +19325,7 @@
       <c r="C89" s="257"/>
       <c r="D89" s="324"/>
       <c r="E89" s="325" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F89" s="325" t="s">
         <v>610</v>
@@ -19371,7 +19344,7 @@
       <c r="C90" s="257"/>
       <c r="D90" s="326"/>
       <c r="E90" s="325" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F90" s="325" t="s">
         <v>629</v>
@@ -19382,10 +19355,10 @@
       </c>
       <c r="I90" s="325"/>
       <c r="J90" s="327" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="K90" s="287" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="13">
@@ -19394,7 +19367,7 @@
       <c r="C91" s="316"/>
       <c r="D91" s="328"/>
       <c r="E91" s="325" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F91" s="325" t="s">
         <v>610</v>
@@ -19404,7 +19377,7 @@
       <c r="I91" s="325"/>
       <c r="J91" s="311"/>
       <c r="K91" s="320" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="13">
@@ -19425,7 +19398,7 @@
         <v>579</v>
       </c>
       <c r="K92" s="320" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="13">
@@ -19446,7 +19419,7 @@
         <v>579</v>
       </c>
       <c r="K93" s="320" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="14">
@@ -19462,10 +19435,10 @@
       <c r="H94" s="325"/>
       <c r="I94" s="325"/>
       <c r="J94" s="311" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="K94" s="320" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="14">
@@ -19473,7 +19446,7 @@
       <c r="B95" s="285"/>
       <c r="C95" s="252"/>
       <c r="D95" s="321" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E95" s="322"/>
       <c r="F95" s="322"/>
@@ -19482,7 +19455,7 @@
       <c r="I95" s="322"/>
       <c r="J95" s="323"/>
       <c r="K95" s="287" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="13">
@@ -19494,7 +19467,7 @@
         <v>557</v>
       </c>
       <c r="F96" s="325" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G96" s="325" t="s">
         <v>559</v>
@@ -19504,10 +19477,10 @@
       </c>
       <c r="I96" s="325"/>
       <c r="J96" s="311" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="K96" s="287" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="13">
@@ -19516,7 +19489,7 @@
       <c r="C97" s="257"/>
       <c r="D97" s="324"/>
       <c r="E97" s="325" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F97" s="325" t="s">
         <v>563</v>
@@ -19528,7 +19501,7 @@
       <c r="I97" s="325"/>
       <c r="J97" s="311"/>
       <c r="K97" s="287" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="13">
@@ -19537,10 +19510,10 @@
       <c r="C98" s="257"/>
       <c r="D98" s="324"/>
       <c r="E98" s="325" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F98" s="325" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G98" s="325"/>
       <c r="H98" s="325" t="s">
@@ -19548,7 +19521,7 @@
       </c>
       <c r="I98" s="325"/>
       <c r="J98" s="311" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="K98" s="287"/>
     </row>
@@ -19558,7 +19531,7 @@
       <c r="C99" s="257"/>
       <c r="D99" s="324"/>
       <c r="E99" s="325" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F99" s="325" t="s">
         <v>617</v>
@@ -19569,10 +19542,10 @@
       </c>
       <c r="I99" s="325"/>
       <c r="J99" s="311" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="K99" s="287" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="13">
@@ -19581,10 +19554,10 @@
       <c r="C100" s="257"/>
       <c r="D100" s="326"/>
       <c r="E100" s="325" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F100" s="325" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G100" s="325"/>
       <c r="H100" s="325" t="s">
@@ -19593,7 +19566,7 @@
       <c r="I100" s="325"/>
       <c r="J100" s="311"/>
       <c r="K100" s="320" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="13">
@@ -19602,7 +19575,7 @@
       <c r="C101" s="316"/>
       <c r="D101" s="328"/>
       <c r="E101" s="325" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F101" s="325" t="s">
         <v>569</v>
@@ -19611,10 +19584,10 @@
       <c r="H101" s="325"/>
       <c r="I101" s="325"/>
       <c r="J101" s="311" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K101" s="320" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="13">
@@ -19635,7 +19608,7 @@
         <v>579</v>
       </c>
       <c r="K102" s="320" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="13">
@@ -19656,7 +19629,7 @@
         <v>579</v>
       </c>
       <c r="K103" s="320" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="13">
@@ -19671,7 +19644,7 @@
       <c r="I104" s="56"/>
       <c r="J104" s="56"/>
       <c r="K104" s="285" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="13">
@@ -19688,7 +19661,7 @@
       <c r="I105" s="56"/>
       <c r="J105" s="56"/>
       <c r="K105" s="285" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="13">
@@ -19705,7 +19678,7 @@
       <c r="I106" s="56"/>
       <c r="J106" s="56"/>
       <c r="K106" s="285" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="13">
@@ -19722,7 +19695,7 @@
       <c r="I107" s="56"/>
       <c r="J107" s="56"/>
       <c r="K107" s="285" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="13">
@@ -19739,7 +19712,7 @@
       <c r="I108" s="56"/>
       <c r="J108" s="56"/>
       <c r="K108" s="285" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="13">
@@ -19756,117 +19729,117 @@
       <c r="I109" s="56"/>
       <c r="J109" s="56"/>
       <c r="K109" s="285" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="15.75" customHeight="1">
       <c r="K111" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="15.75" customHeight="1">
       <c r="K112" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="113" spans="11:11" ht="15.75" customHeight="1">
       <c r="K113" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="114" spans="11:11" ht="15.75" customHeight="1">
       <c r="K114" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="115" spans="11:11" ht="15.75" customHeight="1">
       <c r="K115" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="116" spans="11:11" ht="15.75" customHeight="1">
       <c r="K116" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="117" spans="11:11" ht="15.75" customHeight="1">
       <c r="K117" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="118" spans="11:11" ht="15.75" customHeight="1">
       <c r="K118" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="119" spans="11:11" ht="15.75" customHeight="1">
       <c r="K119" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="120" spans="11:11" ht="15.75" customHeight="1">
       <c r="K120" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="122" spans="11:11" ht="15.75" customHeight="1">
       <c r="K122" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="123" spans="11:11" ht="15.75" customHeight="1">
       <c r="K123" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="124" spans="11:11" ht="15.75" customHeight="1">
       <c r="K124" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="125" spans="11:11" ht="15.75" customHeight="1">
       <c r="K125" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="126" spans="11:11" ht="15.75" customHeight="1">
       <c r="K126" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="127" spans="11:11" ht="15.75" customHeight="1">
       <c r="K127" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="128" spans="11:11" ht="15.75" customHeight="1">
       <c r="K128" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="129" spans="11:11" ht="15.75" customHeight="1">
       <c r="K129" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="130" spans="11:11" ht="15.75" customHeight="1">
       <c r="K130" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="131" spans="11:11" ht="15.75" customHeight="1">
       <c r="K131" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="132" spans="11:11" ht="15.75" customHeight="1">
       <c r="K132" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="133" spans="11:11" ht="15.75" customHeight="1">
       <c r="K133" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -19969,10 +19942,10 @@
         <v>177</v>
       </c>
       <c r="E6" s="265" t="s">
+        <v>866</v>
+      </c>
+      <c r="F6" s="374" t="s">
         <v>867</v>
-      </c>
-      <c r="F6" s="374" t="s">
-        <v>868</v>
       </c>
       <c r="G6" s="265" t="s">
         <v>567</v>
@@ -19990,10 +19963,10 @@
         <v>177</v>
       </c>
       <c r="E7" s="266" t="s">
+        <v>878</v>
+      </c>
+      <c r="F7" s="379" t="s">
         <v>879</v>
-      </c>
-      <c r="F7" s="379" t="s">
-        <v>880</v>
       </c>
       <c r="G7" s="266" t="s">
         <v>567</v>
@@ -20008,13 +19981,13 @@
       <c r="B8" s="259"/>
       <c r="C8" s="259"/>
       <c r="D8" s="267" t="s">
+        <v>903</v>
+      </c>
+      <c r="E8" s="267" t="s">
+        <v>866</v>
+      </c>
+      <c r="F8" s="392" t="s">
         <v>904</v>
-      </c>
-      <c r="E8" s="267" t="s">
-        <v>867</v>
-      </c>
-      <c r="F8" s="392" t="s">
-        <v>905</v>
       </c>
       <c r="G8" s="267" t="s">
         <v>567</v>
@@ -20032,10 +20005,10 @@
         <v>575</v>
       </c>
       <c r="E9" s="266" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F9" s="379" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G9" s="266" t="s">
         <v>567</v>
@@ -20053,7 +20026,7 @@
         <v>578</v>
       </c>
       <c r="E10" s="267" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F10" s="267" t="s">
         <v>460</v>
@@ -20081,7 +20054,7 @@
       <c r="A12" s="139"/>
       <c r="B12" s="259"/>
       <c r="C12" s="260" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D12" s="259"/>
       <c r="E12" s="259"/>
@@ -20122,7 +20095,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="264" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F15" s="259"/>
       <c r="G15" s="259"/>
@@ -20134,10 +20107,10 @@
       <c r="B16" s="259"/>
       <c r="C16" s="259"/>
       <c r="D16" s="265" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E16" s="265" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F16" s="259"/>
       <c r="G16" s="259"/>
@@ -20149,7 +20122,7 @@
       <c r="B17" s="259"/>
       <c r="C17" s="259"/>
       <c r="D17" s="265" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E17" s="265" t="s">
         <v>177</v>
@@ -20179,10 +20152,10 @@
       <c r="B19" s="259"/>
       <c r="C19" s="259"/>
       <c r="D19" s="265" t="s">
+        <v>849</v>
+      </c>
+      <c r="E19" s="265" t="s">
         <v>850</v>
-      </c>
-      <c r="E19" s="265" t="s">
-        <v>851</v>
       </c>
       <c r="F19" s="259"/>
       <c r="G19" s="259"/>
@@ -20197,7 +20170,7 @@
         <v>476</v>
       </c>
       <c r="E20" s="374" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F20" s="259"/>
       <c r="G20" s="259"/>
@@ -20220,7 +20193,7 @@
       <c r="B22" s="259"/>
       <c r="C22" s="259"/>
       <c r="D22" s="371" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E22" s="259"/>
       <c r="F22" s="259"/>
@@ -20233,19 +20206,19 @@
       <c r="B23" s="259"/>
       <c r="C23" s="259"/>
       <c r="D23" s="372" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E23" s="372" t="s">
         <v>550</v>
       </c>
       <c r="F23" s="372" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G23" s="372" t="s">
         <v>476</v>
       </c>
       <c r="H23" s="372" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I23" s="259"/>
     </row>
@@ -20254,19 +20227,19 @@
       <c r="B24" s="259"/>
       <c r="C24" s="259"/>
       <c r="D24" s="265" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E24" s="265" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F24" s="265" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G24" s="374" t="s">
+        <v>872</v>
+      </c>
+      <c r="H24" s="100" t="s">
         <v>873</v>
-      </c>
-      <c r="H24" s="100" t="s">
-        <v>874</v>
       </c>
       <c r="I24" s="259"/>
     </row>
@@ -20275,19 +20248,19 @@
       <c r="B25" s="259"/>
       <c r="C25" s="259"/>
       <c r="D25" s="265" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E25" s="265" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F25" s="265" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G25" s="374" t="s">
+        <v>874</v>
+      </c>
+      <c r="H25" s="375" t="s">
         <v>875</v>
-      </c>
-      <c r="H25" s="375" t="s">
-        <v>876</v>
       </c>
       <c r="I25" s="259"/>
     </row>
@@ -20296,16 +20269,16 @@
       <c r="B26" s="259"/>
       <c r="C26" s="259"/>
       <c r="D26" s="265" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E26" s="265" t="s">
+        <v>855</v>
+      </c>
+      <c r="F26" s="265" t="s">
         <v>856</v>
       </c>
-      <c r="F26" s="265" t="s">
-        <v>857</v>
-      </c>
       <c r="G26" s="376" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H26" s="100">
         <v>2</v>
@@ -20317,16 +20290,16 @@
       <c r="B27" s="259"/>
       <c r="C27" s="259"/>
       <c r="D27" s="265" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E27" s="265" t="s">
+        <v>859</v>
+      </c>
+      <c r="F27" s="265" t="s">
+        <v>856</v>
+      </c>
+      <c r="G27" s="265" t="s">
         <v>860</v>
-      </c>
-      <c r="F27" s="265" t="s">
-        <v>857</v>
-      </c>
-      <c r="G27" s="265" t="s">
-        <v>861</v>
       </c>
       <c r="H27" s="100">
         <v>20</v>
@@ -20349,7 +20322,7 @@
       <c r="B29" s="259"/>
       <c r="C29" s="259"/>
       <c r="D29" s="373" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E29" s="259"/>
       <c r="F29" s="259"/>
@@ -20362,13 +20335,13 @@
       <c r="B30" s="259"/>
       <c r="C30" s="259"/>
       <c r="D30" s="372" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E30" s="372" t="s">
         <v>476</v>
       </c>
       <c r="F30" s="372" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G30" s="259"/>
       <c r="H30" s="259"/>
@@ -20379,13 +20352,13 @@
       <c r="B31" s="259"/>
       <c r="C31" s="259"/>
       <c r="D31" s="265" t="s">
+        <v>864</v>
+      </c>
+      <c r="E31" s="265" t="s">
         <v>865</v>
       </c>
-      <c r="E31" s="265" t="s">
-        <v>866</v>
-      </c>
       <c r="F31" s="265" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G31" s="377"/>
       <c r="H31" s="259"/>
@@ -20396,13 +20369,13 @@
       <c r="B32" s="259"/>
       <c r="C32" s="259"/>
       <c r="D32" s="265" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E32" s="376" t="s">
+        <v>922</v>
+      </c>
+      <c r="F32" s="265" t="s">
         <v>923</v>
-      </c>
-      <c r="F32" s="265" t="s">
-        <v>924</v>
       </c>
       <c r="G32" s="259"/>
       <c r="H32" s="259"/>
@@ -20424,7 +20397,7 @@
       <c r="B34" s="259"/>
       <c r="C34" s="259"/>
       <c r="D34" s="373" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E34" s="259"/>
       <c r="F34" s="259"/>
@@ -20524,7 +20497,7 @@
       <c r="A43" s="139"/>
       <c r="B43" s="259"/>
       <c r="C43" s="260" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D43" s="259"/>
       <c r="E43" s="259"/>
@@ -20538,7 +20511,7 @@
       <c r="B44" s="259"/>
       <c r="C44" s="259"/>
       <c r="D44" s="380" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E44" s="259"/>
       <c r="F44" s="259"/>
@@ -20565,7 +20538,7 @@
         <v>5</v>
       </c>
       <c r="E46" s="264" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F46" s="259"/>
       <c r="G46" s="259"/>
@@ -20577,10 +20550,10 @@
       <c r="B47" s="259"/>
       <c r="C47" s="259"/>
       <c r="D47" s="265" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E47" s="265" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F47" s="259"/>
       <c r="G47" s="259"/>
@@ -20592,7 +20565,7 @@
       <c r="B48" s="259"/>
       <c r="C48" s="259"/>
       <c r="D48" s="265" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E48" s="265" t="s">
         <v>177</v>
@@ -20622,10 +20595,10 @@
       <c r="B50" s="259"/>
       <c r="C50" s="259"/>
       <c r="D50" s="265" t="s">
+        <v>849</v>
+      </c>
+      <c r="E50" s="265" t="s">
         <v>850</v>
-      </c>
-      <c r="E50" s="265" t="s">
-        <v>851</v>
       </c>
       <c r="F50" s="259"/>
       <c r="G50" s="259"/>
@@ -20640,7 +20613,7 @@
         <v>476</v>
       </c>
       <c r="E51" s="374" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F51" s="259"/>
       <c r="G51" s="259"/>
@@ -20663,7 +20636,7 @@
       <c r="B53" s="259"/>
       <c r="C53" s="259"/>
       <c r="D53" s="371" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E53" s="259"/>
       <c r="F53" s="259"/>
@@ -20676,19 +20649,19 @@
       <c r="B54" s="259"/>
       <c r="C54" s="259"/>
       <c r="D54" s="372" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E54" s="372" t="s">
         <v>550</v>
       </c>
       <c r="F54" s="372" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G54" s="372" t="s">
         <v>476</v>
       </c>
       <c r="H54" s="372" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I54" s="259"/>
     </row>
@@ -20697,16 +20670,16 @@
       <c r="B55" s="259"/>
       <c r="C55" s="259"/>
       <c r="D55" s="265" t="s">
+        <v>884</v>
+      </c>
+      <c r="E55" s="265" t="s">
+        <v>889</v>
+      </c>
+      <c r="F55" s="376" t="s">
         <v>885</v>
       </c>
-      <c r="E55" s="265" t="s">
-        <v>890</v>
-      </c>
-      <c r="F55" s="376" t="s">
+      <c r="G55" s="374" t="s">
         <v>886</v>
-      </c>
-      <c r="G55" s="374" t="s">
-        <v>887</v>
       </c>
       <c r="H55" s="100">
         <v>1</v>
@@ -20729,7 +20702,7 @@
       <c r="B57" s="259"/>
       <c r="C57" s="259"/>
       <c r="D57" s="373" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E57" s="259"/>
       <c r="F57" s="259"/>
@@ -20742,13 +20715,13 @@
       <c r="B58" s="259"/>
       <c r="C58" s="259"/>
       <c r="D58" s="372" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E58" s="372" t="s">
         <v>476</v>
       </c>
       <c r="F58" s="372" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G58" s="259"/>
       <c r="H58" s="259"/>
@@ -20759,13 +20732,13 @@
       <c r="B59" s="259"/>
       <c r="C59" s="259"/>
       <c r="D59" s="265" t="s">
+        <v>864</v>
+      </c>
+      <c r="E59" s="265" t="s">
         <v>865</v>
       </c>
-      <c r="E59" s="265" t="s">
-        <v>866</v>
-      </c>
       <c r="F59" s="265" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G59" s="377"/>
       <c r="H59" s="259"/>
@@ -20776,13 +20749,13 @@
       <c r="B60" s="259"/>
       <c r="C60" s="259"/>
       <c r="D60" s="265" t="s">
+        <v>887</v>
+      </c>
+      <c r="E60" s="265" t="s">
         <v>888</v>
       </c>
-      <c r="E60" s="265" t="s">
-        <v>889</v>
-      </c>
       <c r="F60" s="265" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G60" s="259"/>
       <c r="H60" s="259"/>
@@ -20804,7 +20777,7 @@
       <c r="B62" s="259"/>
       <c r="C62" s="259"/>
       <c r="D62" s="373" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E62" s="259"/>
       <c r="F62" s="259"/>
@@ -20893,7 +20866,7 @@
       <c r="A70" s="139"/>
       <c r="B70" s="259"/>
       <c r="C70" s="260" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D70" s="259"/>
       <c r="E70" s="259"/>
@@ -20934,7 +20907,7 @@
         <v>5</v>
       </c>
       <c r="E73" s="395" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F73" s="259"/>
       <c r="G73" s="259"/>
@@ -20946,10 +20919,10 @@
       <c r="B74" s="259"/>
       <c r="C74" s="259"/>
       <c r="D74" s="265" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E74" s="394" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F74" s="259"/>
       <c r="G74" s="259"/>
@@ -20961,10 +20934,10 @@
       <c r="B75" s="259"/>
       <c r="C75" s="259"/>
       <c r="D75" s="265" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E75" s="265" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F75" s="259"/>
       <c r="G75" s="259"/>
@@ -20979,7 +20952,7 @@
         <v>393</v>
       </c>
       <c r="E76" s="265" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F76" s="259"/>
       <c r="G76" s="259"/>
@@ -20991,10 +20964,10 @@
       <c r="B77" s="259"/>
       <c r="C77" s="259"/>
       <c r="D77" s="265" t="s">
+        <v>849</v>
+      </c>
+      <c r="E77" s="265" t="s">
         <v>850</v>
-      </c>
-      <c r="E77" s="265" t="s">
-        <v>851</v>
       </c>
       <c r="F77" s="259"/>
       <c r="G77" s="259"/>
@@ -21009,7 +20982,7 @@
         <v>476</v>
       </c>
       <c r="E78" s="374" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F78" s="382"/>
       <c r="G78" s="259"/>
@@ -21032,7 +21005,7 @@
       <c r="B80" s="259"/>
       <c r="C80" s="259"/>
       <c r="D80" s="383" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E80" s="259"/>
       <c r="F80" s="259"/>
@@ -21045,13 +21018,13 @@
       <c r="B81" s="259"/>
       <c r="C81" s="259"/>
       <c r="D81" s="372" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E81" s="372" t="s">
         <v>550</v>
       </c>
       <c r="F81" s="372" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G81" s="384" t="s">
         <v>476</v>
@@ -21067,13 +21040,13 @@
         <v>621</v>
       </c>
       <c r="E82" s="265" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F82" s="265" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G82" s="398" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H82" s="388">
         <v>5</v>
@@ -21085,16 +21058,16 @@
       <c r="B83" s="259"/>
       <c r="C83" s="259"/>
       <c r="D83" s="265" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E83" s="265" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F83" s="265" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G83" s="398" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H83" s="388">
         <v>5</v>
@@ -21106,16 +21079,16 @@
       <c r="B84" s="259"/>
       <c r="C84" s="259"/>
       <c r="D84" s="265" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E84" s="265" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F84" s="265" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G84" s="397" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H84" s="388">
         <v>5</v>
@@ -21127,16 +21100,16 @@
       <c r="B85" s="259"/>
       <c r="C85" s="259"/>
       <c r="D85" s="265" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E85" s="265" t="s">
         <v>610</v>
       </c>
       <c r="F85" s="265" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G85" s="398" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H85" s="388">
         <v>5</v>
@@ -21148,16 +21121,16 @@
       <c r="B86" s="259"/>
       <c r="C86" s="259"/>
       <c r="D86" s="265" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E86" s="265" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F86" s="265" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G86" s="398" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H86" s="388">
         <v>5</v>
@@ -21169,16 +21142,16 @@
       <c r="B87" s="259"/>
       <c r="C87" s="259"/>
       <c r="D87" s="265" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E87" s="265" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F87" s="265" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G87" s="396" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H87" s="388">
         <v>5</v>
@@ -21190,16 +21163,16 @@
       <c r="B88" s="259"/>
       <c r="C88" s="259"/>
       <c r="D88" s="265" t="s">
+        <v>911</v>
+      </c>
+      <c r="E88" s="265" t="s">
         <v>912</v>
       </c>
-      <c r="E88" s="265" t="s">
-        <v>913</v>
-      </c>
       <c r="F88" s="265" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G88" s="398" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H88" s="388">
         <v>5</v>
@@ -21222,7 +21195,7 @@
       <c r="B90" s="259"/>
       <c r="C90" s="259"/>
       <c r="D90" s="373" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E90" s="259"/>
       <c r="F90" s="259"/>
@@ -21235,13 +21208,13 @@
       <c r="B91" s="259"/>
       <c r="C91" s="259"/>
       <c r="D91" s="372" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E91" s="372" t="s">
         <v>476</v>
       </c>
       <c r="F91" s="372" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G91" s="259"/>
       <c r="H91" s="259"/>
@@ -21252,13 +21225,13 @@
       <c r="B92" s="259"/>
       <c r="C92" s="259"/>
       <c r="D92" s="265" t="s">
+        <v>896</v>
+      </c>
+      <c r="E92" s="265" t="s">
         <v>897</v>
       </c>
-      <c r="E92" s="265" t="s">
-        <v>898</v>
-      </c>
       <c r="F92" s="265" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G92" s="259"/>
       <c r="H92" s="259"/>
@@ -21269,13 +21242,13 @@
       <c r="B93" s="259"/>
       <c r="C93" s="259"/>
       <c r="D93" s="265" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E93" s="376" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F93" s="265" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G93" s="259"/>
       <c r="H93" s="259"/>
@@ -21286,13 +21259,13 @@
       <c r="B94" s="259"/>
       <c r="C94" s="259"/>
       <c r="D94" s="265" t="s">
+        <v>899</v>
+      </c>
+      <c r="E94" s="265" t="s">
         <v>900</v>
       </c>
-      <c r="E94" s="265" t="s">
+      <c r="F94" s="265" t="s">
         <v>901</v>
-      </c>
-      <c r="F94" s="265" t="s">
-        <v>902</v>
       </c>
       <c r="G94" s="259"/>
       <c r="H94" s="259"/>
@@ -21303,7 +21276,7 @@
       <c r="B95" s="259"/>
       <c r="C95" s="259"/>
       <c r="D95" s="259" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E95" s="259"/>
       <c r="F95" s="259"/>
@@ -21337,7 +21310,7 @@
       <c r="A98" s="139"/>
       <c r="C98" s="259"/>
       <c r="D98" s="373" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E98" s="259"/>
       <c r="F98" s="259"/>
@@ -21415,7 +21388,7 @@
       <c r="A105" s="139"/>
       <c r="B105" s="259"/>
       <c r="C105" s="260" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D105" s="259"/>
       <c r="E105" s="259"/>
@@ -21429,7 +21402,7 @@
       <c r="B106" s="259"/>
       <c r="C106" s="259"/>
       <c r="D106" s="380" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E106" s="259"/>
       <c r="F106" s="259"/>
@@ -21456,7 +21429,7 @@
         <v>5</v>
       </c>
       <c r="E108" s="264" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F108" s="259"/>
       <c r="G108" s="259"/>
@@ -21468,10 +21441,10 @@
       <c r="B109" s="259"/>
       <c r="C109" s="259"/>
       <c r="D109" s="265" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E109" s="265" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F109" s="259"/>
       <c r="G109" s="259"/>
@@ -21483,10 +21456,10 @@
       <c r="B110" s="259"/>
       <c r="C110" s="259"/>
       <c r="D110" s="265" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E110" s="265" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="F110" s="259"/>
       <c r="G110" s="259"/>
@@ -21501,7 +21474,7 @@
         <v>393</v>
       </c>
       <c r="E111" s="401" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F111" s="259"/>
       <c r="G111" s="259"/>
@@ -21513,10 +21486,10 @@
       <c r="B112" s="259"/>
       <c r="C112" s="259"/>
       <c r="D112" s="398" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E112" s="403" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F112" s="259"/>
       <c r="G112" s="259"/>
@@ -21531,7 +21504,7 @@
         <v>476</v>
       </c>
       <c r="E113" s="402" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F113" s="382"/>
       <c r="G113" s="259"/>
@@ -21543,7 +21516,7 @@
       <c r="B114" s="259"/>
       <c r="C114" s="259"/>
       <c r="D114" s="405" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E114" s="259"/>
       <c r="F114" s="259"/>
@@ -21567,7 +21540,7 @@
       <c r="B116" s="259"/>
       <c r="C116" s="259"/>
       <c r="D116" s="373" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E116" s="259"/>
       <c r="F116" s="259"/>
@@ -21580,13 +21553,13 @@
       <c r="B117" s="259"/>
       <c r="C117" s="259"/>
       <c r="D117" s="372" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E117" s="372" t="s">
         <v>550</v>
       </c>
       <c r="F117" s="384" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G117" s="399"/>
       <c r="H117" s="387"/>
@@ -21597,13 +21570,13 @@
       <c r="B118" s="259"/>
       <c r="C118" s="259"/>
       <c r="D118" s="265" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E118" s="265" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F118" s="397" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G118" s="404"/>
       <c r="H118" s="400"/>
@@ -21614,13 +21587,13 @@
       <c r="B119" s="259"/>
       <c r="C119" s="259"/>
       <c r="D119" s="265" t="s">
+        <v>887</v>
+      </c>
+      <c r="E119" s="265" t="s">
         <v>888</v>
       </c>
-      <c r="E119" s="265" t="s">
-        <v>889</v>
-      </c>
       <c r="F119" s="397" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G119" s="404"/>
       <c r="H119" s="400"/>
@@ -21631,13 +21604,13 @@
       <c r="B120" s="259"/>
       <c r="C120" s="259"/>
       <c r="D120" s="265" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E120" s="265" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F120" s="397" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G120" s="404"/>
       <c r="H120" s="400"/>
@@ -21648,13 +21621,13 @@
       <c r="B121" s="259"/>
       <c r="C121" s="259"/>
       <c r="D121" s="265" t="s">
+        <v>899</v>
+      </c>
+      <c r="E121" s="265" t="s">
         <v>900</v>
       </c>
-      <c r="E121" s="265" t="s">
-        <v>901</v>
-      </c>
       <c r="F121" s="397" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G121" s="404"/>
       <c r="H121" s="400"/>
@@ -21665,13 +21638,13 @@
       <c r="B122" s="259"/>
       <c r="C122" s="259"/>
       <c r="D122" s="265" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E122" s="374" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F122" s="397" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G122" s="404"/>
       <c r="H122" s="400"/>
@@ -21692,7 +21665,7 @@
       <c r="A124" s="139"/>
       <c r="C124" s="259"/>
       <c r="D124" s="383" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E124" s="259"/>
       <c r="F124" s="259"/>
@@ -21781,7 +21754,7 @@
       <c r="A132" s="139"/>
       <c r="B132" s="259"/>
       <c r="C132" s="260" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D132" s="259"/>
       <c r="E132" s="259"/>
@@ -21822,7 +21795,7 @@
         <v>5</v>
       </c>
       <c r="E135" s="264" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F135" s="259"/>
       <c r="G135" s="259"/>
@@ -21834,10 +21807,10 @@
       <c r="B136" s="259"/>
       <c r="C136" s="259"/>
       <c r="D136" s="265" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E136" s="265" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F136" s="259"/>
       <c r="G136" s="259"/>
@@ -21849,7 +21822,7 @@
       <c r="B137" s="259"/>
       <c r="C137" s="259"/>
       <c r="D137" s="265" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E137" s="265" t="s">
         <v>578</v>
@@ -21867,7 +21840,7 @@
         <v>393</v>
       </c>
       <c r="E138" s="401" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F138" s="259"/>
       <c r="G138" s="259"/>
@@ -21879,10 +21852,10 @@
       <c r="B139" s="259"/>
       <c r="C139" s="259"/>
       <c r="D139" s="397" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E139" s="415" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F139" s="259"/>
       <c r="G139" s="259"/>
@@ -21897,7 +21870,7 @@
         <v>476</v>
       </c>
       <c r="E140" s="414" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F140" s="382"/>
       <c r="G140" s="259"/>
@@ -21920,7 +21893,7 @@
       <c r="B142" s="259"/>
       <c r="C142" s="259"/>
       <c r="D142" s="373" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E142" s="259"/>
       <c r="F142" s="259"/>
@@ -21933,13 +21906,13 @@
       <c r="B143" s="259"/>
       <c r="C143" s="259"/>
       <c r="D143" s="372" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E143" s="372" t="s">
         <v>476</v>
       </c>
       <c r="F143" s="372" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G143" s="259"/>
       <c r="H143" s="259"/>
@@ -21950,13 +21923,13 @@
       <c r="B144" s="259"/>
       <c r="C144" s="259"/>
       <c r="D144" s="265" t="s">
+        <v>945</v>
+      </c>
+      <c r="E144" s="265" t="s">
         <v>946</v>
       </c>
-      <c r="E144" s="265" t="s">
+      <c r="F144" s="265" t="s">
         <v>947</v>
-      </c>
-      <c r="F144" s="265" t="s">
-        <v>948</v>
       </c>
       <c r="G144" s="259"/>
       <c r="H144" s="259"/>
@@ -21967,13 +21940,13 @@
       <c r="B145" s="259"/>
       <c r="C145" s="259"/>
       <c r="D145" s="265" t="s">
+        <v>887</v>
+      </c>
+      <c r="E145" s="265" t="s">
         <v>888</v>
       </c>
-      <c r="E145" s="265" t="s">
-        <v>889</v>
-      </c>
       <c r="F145" s="265" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G145" s="259"/>
       <c r="H145" s="259"/>
@@ -21984,13 +21957,13 @@
       <c r="B146" s="259"/>
       <c r="C146" s="259"/>
       <c r="D146" s="265" t="s">
+        <v>899</v>
+      </c>
+      <c r="E146" s="265" t="s">
         <v>900</v>
       </c>
-      <c r="E146" s="265" t="s">
-        <v>901</v>
-      </c>
       <c r="F146" s="265" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G146" s="259"/>
       <c r="H146" s="259"/>
@@ -22001,13 +21974,13 @@
       <c r="B147" s="259"/>
       <c r="C147" s="259"/>
       <c r="D147" s="394" t="s">
+        <v>930</v>
+      </c>
+      <c r="E147" s="402" t="s">
+        <v>950</v>
+      </c>
+      <c r="F147" s="394" t="s">
         <v>931</v>
-      </c>
-      <c r="E147" s="402" t="s">
-        <v>951</v>
-      </c>
-      <c r="F147" s="394" t="s">
-        <v>932</v>
       </c>
       <c r="G147" s="259"/>
       <c r="H147" s="259"/>
@@ -22028,7 +22001,7 @@
       <c r="A149" s="139"/>
       <c r="C149" s="259"/>
       <c r="D149" s="373" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E149" s="259"/>
       <c r="F149" s="259"/>
@@ -22115,31 +22088,31 @@
         <v>5</v>
       </c>
       <c r="E157" s="264" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15.75" customHeight="1">
       <c r="D158" s="265" t="s">
+        <v>952</v>
+      </c>
+      <c r="E158" s="265" t="s">
         <v>953</v>
-      </c>
-      <c r="E158" s="265" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="32">
       <c r="D159" s="265" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E159" s="265" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15.75" customHeight="1">
       <c r="D160" s="265" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E160" s="265" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="161" spans="3:6" ht="15.75" customHeight="1">
@@ -22148,13 +22121,13 @@
     </row>
     <row r="162" spans="3:6" ht="15.75" customHeight="1">
       <c r="D162" s="373" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E162" s="259"/>
     </row>
     <row r="163" spans="3:6" ht="15.75" customHeight="1">
       <c r="D163" s="406" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E163" s="407" t="s">
         <v>550</v>
@@ -22162,63 +22135,63 @@
     </row>
     <row r="164" spans="3:6" ht="15.75" customHeight="1">
       <c r="D164" s="408" t="s">
+        <v>957</v>
+      </c>
+      <c r="E164" s="409" t="s">
         <v>958</v>
-      </c>
-      <c r="E164" s="409" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="165" spans="3:6" ht="15.75" customHeight="1">
       <c r="D165" s="410" t="s">
+        <v>959</v>
+      </c>
+      <c r="E165" s="411" t="s">
         <v>960</v>
-      </c>
-      <c r="E165" s="411" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="166" spans="3:6" ht="15.75" customHeight="1">
       <c r="D166" s="410" t="s">
+        <v>961</v>
+      </c>
+      <c r="E166" s="411" t="s">
         <v>962</v>
-      </c>
-      <c r="E166" s="411" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="167" spans="3:6" ht="15.75" customHeight="1">
       <c r="D167" s="410" t="s">
+        <v>963</v>
+      </c>
+      <c r="E167" s="411" t="s">
         <v>964</v>
-      </c>
-      <c r="E167" s="411" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="168" spans="3:6" ht="15.75" customHeight="1">
       <c r="D168" s="410" t="s">
+        <v>965</v>
+      </c>
+      <c r="E168" s="411" t="s">
         <v>966</v>
-      </c>
-      <c r="E168" s="411" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="169" spans="3:6" ht="15.75" customHeight="1">
       <c r="D169" s="410" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E169" s="411" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="170" spans="3:6" ht="15.75" customHeight="1">
       <c r="D170" s="412" t="s">
+        <v>968</v>
+      </c>
+      <c r="E170" s="413" t="s">
         <v>969</v>
-      </c>
-      <c r="E170" s="413" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="173" spans="3:6" ht="15.75" customHeight="1">
       <c r="C173" s="260" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D173" s="259"/>
       <c r="E173" s="259"/>
@@ -22227,7 +22200,7 @@
     <row r="174" spans="3:6" ht="15.75" customHeight="1">
       <c r="C174" s="259"/>
       <c r="D174" s="373" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E174" s="259"/>
       <c r="F174" s="259"/>
@@ -22235,78 +22208,78 @@
     <row r="175" spans="3:6" ht="15.75" customHeight="1">
       <c r="C175" s="259"/>
       <c r="D175" s="372" t="s">
+        <v>975</v>
+      </c>
+      <c r="E175" s="372" t="s">
         <v>976</v>
       </c>
-      <c r="E175" s="372" t="s">
+      <c r="F175" s="372" t="s">
         <v>977</v>
-      </c>
-      <c r="F175" s="372" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="176" spans="3:6" ht="48">
       <c r="C176" s="259"/>
       <c r="D176" s="265" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E176" s="100">
         <v>404</v>
       </c>
       <c r="F176" s="265" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="177" spans="3:7" ht="15.75" customHeight="1">
       <c r="C177" s="259"/>
       <c r="D177" s="265" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E177" s="100">
         <v>422</v>
       </c>
       <c r="F177" s="265" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="178" spans="3:7" ht="15.75" customHeight="1">
       <c r="C178" s="259"/>
       <c r="D178" s="265" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E178" s="100">
         <v>401</v>
       </c>
       <c r="F178" s="265" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="179" spans="3:7" ht="32">
       <c r="C179" s="259"/>
       <c r="D179" s="394" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E179" s="416">
         <v>403</v>
       </c>
       <c r="F179" s="394" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="181" spans="3:7" ht="15.75" customHeight="1">
       <c r="C181" s="260" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="182" spans="3:7" ht="15.75" customHeight="1">
       <c r="D182" s="417" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E182" s="385"/>
       <c r="F182" s="385"/>
     </row>
     <row r="183" spans="3:7" ht="15.75" customHeight="1">
       <c r="D183" s="420" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E183" s="421"/>
       <c r="F183" s="421"/>
@@ -22314,33 +22287,33 @@
     </row>
     <row r="185" spans="3:7" ht="15.75" customHeight="1">
       <c r="D185" s="264" t="s">
+        <v>983</v>
+      </c>
+      <c r="E185" s="264" t="s">
         <v>984</v>
       </c>
-      <c r="E185" s="264" t="s">
+      <c r="F185" s="264" t="s">
         <v>985</v>
-      </c>
-      <c r="F185" s="264" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="186" spans="3:7" ht="15.75" customHeight="1">
       <c r="D186" s="265" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E186" s="265" t="s">
         <v>557</v>
       </c>
       <c r="F186" s="265" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="187" spans="3:7" ht="15.75" customHeight="1">
       <c r="D187" s="265"/>
       <c r="E187" s="265" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F187" s="265" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="188" spans="3:7" ht="15.75" customHeight="1">
@@ -22349,7 +22322,7 @@
         <v>622</v>
       </c>
       <c r="F188" s="265" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="189" spans="3:7" ht="15.75" customHeight="1">
@@ -22358,7 +22331,7 @@
         <v>623</v>
       </c>
       <c r="F189" s="265" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="190" spans="3:7" ht="15.75" customHeight="1">
@@ -22367,7 +22340,7 @@
         <v>625</v>
       </c>
       <c r="F190" s="265" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="191" spans="3:7" ht="15.75" customHeight="1">
@@ -22376,7 +22349,7 @@
         <v>626</v>
       </c>
       <c r="F191" s="265" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="192" spans="3:7" ht="48">
@@ -22385,7 +22358,7 @@
         <v>613</v>
       </c>
       <c r="F192" s="265" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
   </sheetData>
@@ -22465,10 +22438,10 @@
       <c r="D5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="434" t="s">
+      <c r="E5" s="454" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="435"/>
+      <c r="F5" s="455"/>
       <c r="G5" s="40"/>
       <c r="H5" s="42"/>
       <c r="I5" s="42"/>
@@ -24673,12 +24646,12 @@
       <c r="D29" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="436" t="s">
+      <c r="E29" s="456" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="437"/>
-      <c r="G29" s="437"/>
-      <c r="H29" s="435"/>
+      <c r="F29" s="457"/>
+      <c r="G29" s="457"/>
+      <c r="H29" s="455"/>
       <c r="I29" s="13"/>
     </row>
     <row r="30" spans="1:9" ht="13">
@@ -35294,7 +35267,7 @@
         <v>290</v>
       </c>
       <c r="F7" s="354" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G7" s="166" t="s">
         <v>18</v>
@@ -35347,7 +35320,7 @@
         <v>329</v>
       </c>
       <c r="F10" s="354" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G10" s="166" t="s">
         <v>18</v>
@@ -35391,7 +35364,7 @@
       <c r="A13" s="140"/>
       <c r="B13" s="142"/>
       <c r="C13" s="355" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D13" s="187" t="s">
         <v>280</v>
@@ -35451,7 +35424,7 @@
         <v>346</v>
       </c>
       <c r="F16" s="354" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G16" s="190" t="s">
         <v>104</v>
@@ -35485,7 +35458,7 @@
         <v>354</v>
       </c>
       <c r="F18" s="164" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G18" s="190" t="s">
         <v>104</v>
@@ -35502,7 +35475,7 @@
         <v>359</v>
       </c>
       <c r="F19" s="426" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G19" s="364" t="s">
         <v>104</v>
@@ -35513,13 +35486,13 @@
       <c r="B20" s="142"/>
       <c r="C20" s="361"/>
       <c r="D20" s="365" t="s">
+        <v>818</v>
+      </c>
+      <c r="E20" s="366" t="s">
         <v>819</v>
       </c>
-      <c r="E20" s="366" t="s">
-        <v>820</v>
-      </c>
       <c r="F20" s="367" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G20" s="368" t="s">
         <v>104</v>
@@ -35572,7 +35545,7 @@
         <v>368</v>
       </c>
       <c r="F23" s="354" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G23" s="166" t="s">
         <v>18</v>
@@ -35589,7 +35562,7 @@
         <v>371</v>
       </c>
       <c r="F24" s="354" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G24" s="166" t="s">
         <v>18</v>
@@ -35623,7 +35596,7 @@
         <v>378</v>
       </c>
       <c r="F26" s="354" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G26" s="166" t="s">
         <v>18</v>
@@ -35657,7 +35630,7 @@
         <v>386</v>
       </c>
       <c r="F28" s="356" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G28" s="178" t="s">
         <v>18</v>
@@ -35676,7 +35649,7 @@
         <v>342</v>
       </c>
       <c r="F29" s="358" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G29" s="188" t="s">
         <v>18</v>
@@ -35693,7 +35666,7 @@
         <v>395</v>
       </c>
       <c r="F30" s="354" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G30" s="166" t="s">
         <v>18</v>
@@ -35710,7 +35683,7 @@
         <v>401</v>
       </c>
       <c r="F31" s="186" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G31" s="198" t="s">
         <v>104</v>
@@ -35729,7 +35702,7 @@
         <v>381</v>
       </c>
       <c r="F32" s="358" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G32" s="188" t="s">
         <v>18</v>
@@ -35740,13 +35713,13 @@
       <c r="B33" s="142"/>
       <c r="C33" s="195"/>
       <c r="D33" s="357" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E33" s="173" t="s">
         <v>404</v>
       </c>
       <c r="F33" s="356" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G33" s="178" t="s">
         <v>18</v>
@@ -35765,7 +35738,7 @@
         <v>373</v>
       </c>
       <c r="F34" s="358" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G34" s="188" t="s">
         <v>18</v>
@@ -35776,13 +35749,13 @@
       <c r="B35" s="142"/>
       <c r="C35" s="195"/>
       <c r="D35" s="357" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E35" s="173" t="s">
         <v>408</v>
       </c>
       <c r="F35" s="356" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G35" s="178" t="s">
         <v>18</v>
@@ -35899,13 +35872,13 @@
       <c r="B42" s="142"/>
       <c r="C42" s="195"/>
       <c r="D42" s="357" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E42" s="173" t="s">
         <v>434</v>
       </c>
       <c r="F42" s="356" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G42" s="178" t="s">
         <v>18</v>
@@ -35943,7 +35916,7 @@
         <v>427</v>
       </c>
       <c r="F44" s="358" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G44" s="188" t="s">
         <v>18</v>
@@ -35954,13 +35927,13 @@
       <c r="B45" s="142"/>
       <c r="C45" s="195"/>
       <c r="D45" s="357" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E45" s="173" t="s">
         <v>439</v>
       </c>
       <c r="F45" s="356" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G45" s="178" t="s">
         <v>18</v>
@@ -35990,13 +35963,13 @@
       <c r="B47" s="142"/>
       <c r="C47" s="195"/>
       <c r="D47" s="357" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E47" s="173" t="s">
         <v>442</v>
       </c>
       <c r="F47" s="356" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G47" s="178" t="s">
         <v>18</v>
@@ -36015,7 +35988,7 @@
         <v>444</v>
       </c>
       <c r="F48" s="353" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G48" s="226" t="s">
         <v>18</v>
@@ -36034,7 +36007,7 @@
         <v>447</v>
       </c>
       <c r="F49" s="353" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G49" s="229" t="s">
         <v>104</v>
@@ -36072,7 +36045,7 @@
         <v>453</v>
       </c>
       <c r="F51" s="182" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G51" s="188" t="s">
         <v>18</v>
@@ -36089,7 +36062,7 @@
         <v>455</v>
       </c>
       <c r="F52" s="164" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G52" s="166" t="s">
         <v>18</v>
@@ -36106,7 +36079,7 @@
         <v>457</v>
       </c>
       <c r="F53" s="354" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G53" s="166" t="s">
         <v>18</v>
@@ -36123,7 +36096,7 @@
         <v>459</v>
       </c>
       <c r="F54" s="354" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G54" s="166" t="s">
         <v>18</v>
@@ -36140,7 +36113,7 @@
         <v>461</v>
       </c>
       <c r="F55" s="354" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G55" s="166" t="s">
         <v>18</v>
@@ -36176,7 +36149,7 @@
         <v>468</v>
       </c>
       <c r="F57" s="358" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G57" s="235" t="s">
         <v>104</v>
@@ -36193,7 +36166,7 @@
         <v>474</v>
       </c>
       <c r="F58" s="354" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G58" s="190" t="s">
         <v>104</v>
@@ -36204,13 +36177,13 @@
       <c r="B59" s="140"/>
       <c r="C59" s="231"/>
       <c r="D59" s="237" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E59" s="161" t="s">
         <v>477</v>
       </c>
       <c r="F59" s="354" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G59" s="190" t="s">
         <v>104</v>
@@ -36238,13 +36211,13 @@
       <c r="B61" s="140"/>
       <c r="C61" s="231"/>
       <c r="D61" s="237" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E61" s="161" t="s">
         <v>492</v>
       </c>
       <c r="F61" s="354" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G61" s="190" t="s">
         <v>104</v>
@@ -36291,13 +36264,13 @@
       <c r="B64" s="140"/>
       <c r="C64" s="244"/>
       <c r="D64" s="211" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E64" s="173" t="s">
         <v>530</v>
       </c>
       <c r="F64" s="356" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G64" s="198" t="s">
         <v>104</v>
@@ -36316,7 +36289,7 @@
         <v>485</v>
       </c>
       <c r="F65" s="358" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G65" s="235" t="s">
         <v>104</v>
@@ -36327,13 +36300,13 @@
       <c r="B66" s="140"/>
       <c r="C66" s="244"/>
       <c r="D66" s="211" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E66" s="173" t="s">
         <v>541</v>
       </c>
       <c r="F66" s="356" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G66" s="198" t="s">
         <v>104</v>
@@ -36346,13 +36319,13 @@
         <v>542</v>
       </c>
       <c r="D67" s="233" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E67" s="181" t="s">
         <v>543</v>
       </c>
       <c r="F67" s="358" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G67" s="235" t="s">
         <v>104</v>
@@ -36363,13 +36336,13 @@
       <c r="B68" s="140"/>
       <c r="C68" s="244"/>
       <c r="D68" s="211" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E68" s="173" t="s">
         <v>544</v>
       </c>
       <c r="F68" s="356" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G68" s="198" t="s">
         <v>104</v>
@@ -36444,8 +36417,8 @@
     <row r="3" spans="1:6" ht="14">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="447" t="s">
-        <v>1075</v>
+      <c r="C3" s="458" t="s">
+        <v>1074</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="13"/>
@@ -36704,7 +36677,7 @@
         <v>601</v>
       </c>
       <c r="F24" s="303" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
@@ -36752,64 +36725,64 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="C29" s="296"/>
       <c r="D29" s="306" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E29" s="337" t="s">
+        <v>772</v>
+      </c>
+      <c r="F29" s="307" t="s">
         <v>773</v>
       </c>
-      <c r="F29" s="307" t="s">
-        <v>774</v>
-      </c>
       <c r="G29" s="428" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="14">
       <c r="C30" s="296"/>
       <c r="D30" s="302"/>
       <c r="E30" s="339" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F30" s="340" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="G30" s="427" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="14">
       <c r="C31" s="296"/>
       <c r="D31" s="302"/>
       <c r="E31" s="337" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F31" s="340" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G31" s="429" t="s">
         <v>1009</v>
-      </c>
-      <c r="G31" s="429" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="C32" s="296"/>
       <c r="D32" s="302"/>
       <c r="E32" s="337" t="s">
+        <v>776</v>
+      </c>
+      <c r="F32" s="308" t="s">
         <v>777</v>
-      </c>
-      <c r="F32" s="308" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="33" spans="3:7" ht="15.75" customHeight="1">
       <c r="C33" s="296"/>
       <c r="D33" s="306" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E33" s="342" t="s">
         <v>628</v>
       </c>
       <c r="F33" s="303" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="34" spans="3:7" ht="15.75" customHeight="1">
@@ -36819,13 +36792,13 @@
         <v>608</v>
       </c>
       <c r="F34" s="303" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="35" spans="3:7" ht="15.75" customHeight="1">
       <c r="C35" s="296"/>
       <c r="D35" s="306" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E35" s="343" t="s">
         <v>621</v>
@@ -36851,10 +36824,10 @@
         <v>623</v>
       </c>
       <c r="F37" s="307" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G37" s="427" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="38" spans="3:7" ht="14">
@@ -36864,10 +36837,10 @@
         <v>625</v>
       </c>
       <c r="F38" s="346" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G38" s="427" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="39" spans="3:7" ht="15.75" customHeight="1">
@@ -36877,7 +36850,7 @@
         <v>626</v>
       </c>
       <c r="F39" s="307" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G39" s="427"/>
     </row>
@@ -36888,7 +36861,7 @@
         <v>627</v>
       </c>
       <c r="F40" s="307" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="G40" s="427"/>
     </row>
@@ -36899,7 +36872,7 @@
         <v>613</v>
       </c>
       <c r="F41" s="352" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G41" s="427"/>
     </row>
@@ -36907,17 +36880,17 @@
       <c r="C42" s="296"/>
       <c r="D42" s="332"/>
       <c r="E42" s="345" t="s">
-        <v>797</v>
-      </c>
-      <c r="F42" s="457" t="s">
-        <v>1107</v>
+        <v>796</v>
+      </c>
+      <c r="F42" s="452" t="s">
+        <v>1106</v>
       </c>
       <c r="G42" s="427"/>
     </row>
     <row r="43" spans="3:7" ht="15.75" customHeight="1">
       <c r="C43" s="296"/>
       <c r="D43" s="306" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E43" s="343" t="s">
         <v>621</v>
@@ -36945,10 +36918,10 @@
         <v>623</v>
       </c>
       <c r="F45" s="307" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G45" s="433" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="46" spans="3:7" ht="14">
@@ -36958,10 +36931,10 @@
         <v>625</v>
       </c>
       <c r="F46" s="346" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G46" s="427" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="47" spans="3:7" ht="15.75" customHeight="1">
@@ -36971,7 +36944,7 @@
         <v>626</v>
       </c>
       <c r="F47" s="310" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="48" spans="3:7" ht="15.75" customHeight="1">
@@ -36981,7 +36954,7 @@
         <v>627</v>
       </c>
       <c r="F48" s="307" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="49" spans="3:7" ht="15.75" customHeight="1">
@@ -36990,30 +36963,30 @@
       <c r="E49" s="345" t="s">
         <v>613</v>
       </c>
-      <c r="F49" s="458" t="s">
-        <v>1109</v>
+      <c r="F49" s="453" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="50" spans="3:7" ht="15">
       <c r="C50" s="296"/>
       <c r="D50" s="332"/>
       <c r="E50" s="345" t="s">
-        <v>797</v>
-      </c>
-      <c r="F50" s="457" t="s">
-        <v>1107</v>
+        <v>796</v>
+      </c>
+      <c r="F50" s="452" t="s">
+        <v>1106</v>
       </c>
     </row>
     <row r="51" spans="3:7" ht="15.75" customHeight="1">
       <c r="C51" s="296"/>
       <c r="D51" s="306" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E51" s="342" t="s">
         <v>628</v>
       </c>
       <c r="F51" s="303" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="52" spans="3:7" ht="15.75" customHeight="1">
@@ -37023,146 +36996,146 @@
         <v>608</v>
       </c>
       <c r="F52" s="303" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="53" spans="3:7" ht="15">
       <c r="C53" s="296"/>
       <c r="D53" s="347" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E53" s="345" t="s">
         <v>604</v>
       </c>
       <c r="F53" s="303" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="54" spans="3:7" ht="15">
       <c r="C54" s="296"/>
       <c r="D54" s="341" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E54" s="345" t="s">
         <v>604</v>
       </c>
       <c r="F54" s="303" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="55" spans="3:7" ht="15.75" customHeight="1">
       <c r="C55" s="296"/>
       <c r="D55" s="348" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E55" s="344" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F55" s="333" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G55" s="428" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="56" spans="3:7" ht="15.75" customHeight="1">
       <c r="C56" s="300"/>
       <c r="D56" s="349" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E56" s="334" t="s">
         <v>640</v>
       </c>
       <c r="F56" s="335" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="G56" s="427" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="57" spans="3:7" ht="15.75" customHeight="1">
       <c r="C57" s="301"/>
       <c r="D57" s="336"/>
       <c r="E57" s="334" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F57" s="350" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="58" spans="3:7" ht="15.75" customHeight="1">
       <c r="C58" s="301"/>
       <c r="D58" s="351" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E58" s="334" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F58" s="350" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="59" spans="3:7" ht="15.75" customHeight="1">
       <c r="C59" s="301"/>
       <c r="D59" s="306" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E59" s="337" t="s">
+        <v>772</v>
+      </c>
+      <c r="F59" s="307" t="s">
         <v>773</v>
-      </c>
-      <c r="F59" s="307" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="60" spans="3:7" ht="14">
       <c r="C60" s="301"/>
       <c r="D60" s="302"/>
       <c r="E60" s="339" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F60" s="340" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="61" spans="3:7" ht="14">
       <c r="C61" s="301"/>
       <c r="D61" s="302"/>
       <c r="E61" s="337" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F61" s="340" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G61" s="430" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="62" spans="3:7" ht="15.75" customHeight="1">
       <c r="C62" s="301"/>
       <c r="D62" s="302"/>
       <c r="E62" s="337" t="s">
+        <v>776</v>
+      </c>
+      <c r="F62" s="308" t="s">
         <v>777</v>
-      </c>
-      <c r="F62" s="308" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="63" spans="3:7" ht="15.75" customHeight="1">
       <c r="C63" s="301"/>
       <c r="D63" s="304"/>
       <c r="E63" s="337" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F63" s="308" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G63" s="427" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="64" spans="3:7" ht="15.75" customHeight="1">
       <c r="D64" s="306" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E64" s="343" t="s">
         <v>621</v>
@@ -37186,7 +37159,7 @@
         <v>623</v>
       </c>
       <c r="F66" s="307" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="67" spans="3:7" ht="15.75" customHeight="1">
@@ -37195,7 +37168,7 @@
         <v>625</v>
       </c>
       <c r="F67" s="303" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="68" spans="3:7" ht="15.75" customHeight="1">
@@ -37204,7 +37177,7 @@
         <v>626</v>
       </c>
       <c r="F68" s="307" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="69" spans="3:7" ht="15.75" customHeight="1">
@@ -37213,7 +37186,7 @@
         <v>627</v>
       </c>
       <c r="F69" s="307" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="70" spans="3:7" ht="15.75" customHeight="1">
@@ -37223,7 +37196,7 @@
         <v>613</v>
       </c>
       <c r="F70" s="352" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G70" s="427"/>
     </row>
@@ -37231,16 +37204,16 @@
       <c r="C71" s="296"/>
       <c r="D71" s="332"/>
       <c r="E71" s="345" t="s">
-        <v>797</v>
-      </c>
-      <c r="F71" s="457" t="s">
-        <v>1107</v>
+        <v>796</v>
+      </c>
+      <c r="F71" s="452" t="s">
+        <v>1106</v>
       </c>
       <c r="G71" s="427"/>
     </row>
     <row r="72" spans="3:7" ht="15.75" customHeight="1">
       <c r="D72" s="306" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E72" s="343" t="s">
         <v>621</v>
@@ -37264,7 +37237,7 @@
         <v>623</v>
       </c>
       <c r="F74" s="307" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="75" spans="3:7" ht="15.75" customHeight="1">
@@ -37273,7 +37246,7 @@
         <v>625</v>
       </c>
       <c r="F75" s="303" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="76" spans="3:7" ht="15.75" customHeight="1">
@@ -37282,7 +37255,7 @@
         <v>626</v>
       </c>
       <c r="F76" s="307" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="77" spans="3:7" ht="15.75" customHeight="1">
@@ -37291,7 +37264,7 @@
         <v>627</v>
       </c>
       <c r="F77" s="307" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="78" spans="3:7" ht="15.75" customHeight="1">
@@ -37301,7 +37274,7 @@
         <v>613</v>
       </c>
       <c r="F78" s="352" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G78" s="427"/>
     </row>
@@ -37309,16 +37282,16 @@
       <c r="C79" s="296"/>
       <c r="D79" s="332"/>
       <c r="E79" s="345" t="s">
-        <v>797</v>
-      </c>
-      <c r="F79" s="457" t="s">
-        <v>1107</v>
+        <v>796</v>
+      </c>
+      <c r="F79" s="452" t="s">
+        <v>1106</v>
       </c>
       <c r="G79" s="427"/>
     </row>
     <row r="82" spans="3:6" ht="15.75" customHeight="1">
       <c r="C82" s="422" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D82" s="423"/>
       <c r="E82" s="297"/>
@@ -37330,902 +37303,902 @@
         <v>599</v>
       </c>
       <c r="E83" s="369" t="s">
+        <v>836</v>
+      </c>
+      <c r="F83" s="370" t="s">
         <v>837</v>
       </c>
-      <c r="F83" s="370" t="s">
-        <v>838</v>
-      </c>
     </row>
     <row r="84" spans="3:6" ht="15.75" customHeight="1">
-      <c r="D84" s="459" t="s">
+      <c r="D84" s="302" t="s">
         <v>611</v>
       </c>
-      <c r="E84" s="460" t="s">
+      <c r="E84" s="337" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F84" s="431" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="85" spans="3:6" ht="15.75" customHeight="1">
+      <c r="D85" s="302"/>
+      <c r="E85" s="337" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F85" s="305" t="s">
         <v>1114</v>
       </c>
-      <c r="F84" s="461" t="s">
+    </row>
+    <row r="86" spans="3:6" ht="15.75" customHeight="1">
+      <c r="D86" s="304"/>
+      <c r="E86" s="338" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F86" s="305" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="87" spans="3:6" ht="15.75" customHeight="1">
+      <c r="D87" s="306" t="s">
+        <v>612</v>
+      </c>
+      <c r="E87" s="338" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F87" s="434" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="88" spans="3:6" ht="15.75" customHeight="1">
+      <c r="D88" s="302"/>
+      <c r="E88" s="338" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F88" s="307" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="89" spans="3:6" ht="15.75" customHeight="1">
+      <c r="D89" s="302"/>
+      <c r="E89" s="339" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="85" spans="3:6" ht="15.75" customHeight="1">
-      <c r="D85" s="459"/>
-      <c r="E85" s="460" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F85" s="462" t="s">
+      <c r="F89" s="434" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="90" spans="3:6" ht="15.75" customHeight="1">
+      <c r="D90" s="302"/>
+      <c r="E90" s="339" t="s">
         <v>1115</v>
       </c>
-    </row>
-    <row r="86" spans="3:6" ht="15.75" customHeight="1">
-      <c r="D86" s="463"/>
-      <c r="E86" s="464" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F86" s="462" t="s">
+      <c r="F90" s="434" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="91" spans="3:6" ht="15.75" customHeight="1">
+      <c r="D91" s="302"/>
+      <c r="E91" s="339" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F91" s="434" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="92" spans="3:6" ht="15.75" customHeight="1">
+      <c r="D92" s="302"/>
+      <c r="E92" s="338" t="s">
         <v>1118</v>
       </c>
-    </row>
-    <row r="87" spans="3:6" ht="15.75" customHeight="1">
-      <c r="D87" s="465" t="s">
-        <v>612</v>
-      </c>
-      <c r="E87" s="464" t="s">
-        <v>1123</v>
-      </c>
-      <c r="F87" s="466" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="88" spans="3:6" ht="15.75" customHeight="1">
-      <c r="D88" s="459"/>
-      <c r="E88" s="464" t="s">
-        <v>1056</v>
-      </c>
-      <c r="F88" s="467" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="89" spans="3:6" ht="15.75" customHeight="1">
-      <c r="D89" s="459"/>
-      <c r="E89" s="468" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F89" s="466" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="90" spans="3:6" ht="15.75" customHeight="1">
-      <c r="D90" s="459"/>
-      <c r="E90" s="468" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F90" s="466" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="91" spans="3:6" ht="15.75" customHeight="1">
-      <c r="D91" s="459"/>
-      <c r="E91" s="468" t="s">
+      <c r="F92" s="434" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="93" spans="3:6" ht="15.75" customHeight="1">
+      <c r="D93" s="302"/>
+      <c r="E93" s="338" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F93" s="434" t="s">
         <v>1125</v>
       </c>
-      <c r="F91" s="466" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="92" spans="3:6" ht="15.75" customHeight="1">
-      <c r="D92" s="459"/>
-      <c r="E92" s="464" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F92" s="466" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="93" spans="3:6" ht="15.75" customHeight="1">
-      <c r="D93" s="459"/>
-      <c r="E93" s="464" t="s">
+    </row>
+    <row r="94" spans="3:6" ht="15.75" customHeight="1">
+      <c r="D94" s="309"/>
+      <c r="E94" s="338" t="s">
         <v>1128</v>
       </c>
-      <c r="F93" s="466" t="s">
+      <c r="F94" s="434" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="94" spans="3:6" ht="15.75" customHeight="1">
-      <c r="D94" s="469"/>
-      <c r="E94" s="464" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F94" s="466" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="95" spans="3:6" ht="15.75" customHeight="1">
       <c r="D95" s="306" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E95" s="337" t="s">
+        <v>999</v>
+      </c>
+      <c r="F95" s="424" t="s">
         <v>1000</v>
-      </c>
-      <c r="F95" s="424" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="96" spans="3:6" ht="15.75" customHeight="1">
       <c r="D96" s="302"/>
       <c r="E96" s="339" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F96" s="425" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="97" spans="4:6" ht="15.75" customHeight="1">
       <c r="D97" s="306" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E97" s="342" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F97" s="432" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="98" spans="4:6" ht="15.75" customHeight="1">
       <c r="D98" s="302"/>
       <c r="E98" s="342" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F98" s="303" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="99" spans="4:6" ht="15.75" customHeight="1">
       <c r="D99" s="302"/>
       <c r="E99" s="338" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F99" s="431" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="100" spans="4:6" ht="15.75" customHeight="1">
       <c r="D100" s="309"/>
       <c r="E100" s="338" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F100" s="303" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="101" spans="4:6" ht="15.75" customHeight="1">
       <c r="D101" s="306" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E101" s="343" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F101" s="431" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="102" spans="4:6" ht="15.75" customHeight="1">
       <c r="D102" s="302"/>
       <c r="E102" s="343" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F102" s="303" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="103" spans="4:6" ht="15.75" customHeight="1">
       <c r="D103" s="302"/>
       <c r="E103" s="338" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F103" s="431" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="104" spans="4:6" ht="15.75" customHeight="1">
       <c r="D104" s="331"/>
       <c r="E104" s="338" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F104" s="303" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="105" spans="4:6" ht="15.75" customHeight="1">
       <c r="D105" s="331"/>
       <c r="E105" s="345" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F105" s="303" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="106" spans="4:6" ht="15.75" customHeight="1">
       <c r="D106" s="331"/>
       <c r="E106" s="345" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F106" s="303" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="107" spans="4:6" ht="15.75" customHeight="1">
       <c r="D107" s="331"/>
       <c r="E107" s="345" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F107" s="307" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="108" spans="4:6" ht="15.75" customHeight="1">
       <c r="D108" s="331"/>
       <c r="E108" s="345" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F108" s="431" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="109" spans="4:6" ht="15.75" customHeight="1">
       <c r="D109" s="331"/>
       <c r="E109" s="345" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F109" s="431" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="110" spans="4:6" ht="15.75" customHeight="1">
       <c r="D110" s="331"/>
       <c r="E110" s="345" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F110" s="438" t="s">
         <v>1042</v>
+      </c>
+      <c r="F110" s="434" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="111" spans="4:6" ht="15.75" customHeight="1">
       <c r="D111" s="331"/>
       <c r="E111" s="345" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F111" s="438" t="s">
-        <v>1045</v>
+        <v>1048</v>
+      </c>
+      <c r="F111" s="434" t="s">
+        <v>1044</v>
       </c>
     </row>
     <row r="112" spans="4:6" ht="15.75" customHeight="1">
       <c r="D112" s="331"/>
       <c r="E112" s="345" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F112" s="307" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="113" spans="4:6" ht="15.75" customHeight="1">
       <c r="D113" s="331"/>
       <c r="E113" s="345" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="F113" s="352" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="114" spans="4:6" ht="15.75" customHeight="1">
       <c r="D114" s="331"/>
       <c r="E114" s="345" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="F114" s="305" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="115" spans="4:6" ht="15.75" customHeight="1">
       <c r="D115" s="306" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E115" s="343" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F115" s="431" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="116" spans="4:6" ht="15.75" customHeight="1">
       <c r="D116" s="302"/>
       <c r="E116" s="343" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F116" s="303" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="117" spans="4:6" ht="15.75" customHeight="1">
       <c r="D117" s="302"/>
       <c r="E117" s="338" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F117" s="431" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="118" spans="4:6" ht="15.75" customHeight="1">
       <c r="D118" s="331"/>
       <c r="E118" s="338" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F118" s="303" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="119" spans="4:6" ht="15.75" customHeight="1">
       <c r="D119" s="331"/>
       <c r="E119" s="345" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F119" s="303" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="120" spans="4:6" ht="15.75" customHeight="1">
       <c r="D120" s="331"/>
       <c r="E120" s="345" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F120" s="303" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="121" spans="4:6" ht="15.75" customHeight="1">
       <c r="D121" s="331"/>
       <c r="E121" s="345" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F121" s="307" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="122" spans="4:6" ht="15.75" customHeight="1">
       <c r="D122" s="331"/>
       <c r="E122" s="345" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F122" s="431" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="123" spans="4:6" ht="15.75" customHeight="1">
       <c r="D123" s="331"/>
       <c r="E123" s="345" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F123" s="431" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="124" spans="4:6" ht="15.75" customHeight="1">
       <c r="D124" s="331"/>
       <c r="E124" s="345" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F124" s="424" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="125" spans="4:6" ht="15.75" customHeight="1">
       <c r="D125" s="331"/>
       <c r="E125" s="345" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F125" s="307" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="126" spans="4:6" ht="15.75" customHeight="1">
       <c r="D126" s="331"/>
       <c r="E126" s="345" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F126" s="307" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="127" spans="4:6" ht="15.75" customHeight="1">
       <c r="D127" s="331"/>
       <c r="E127" s="345" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="F127" s="352" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="128" spans="4:6" ht="15.75" customHeight="1">
       <c r="D128" s="331"/>
       <c r="E128" s="345" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="F128" s="305" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="129" spans="4:6" ht="15.75" customHeight="1">
       <c r="D129" s="306" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E129" s="342" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F129" s="432" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="130" spans="4:6" ht="15.75" customHeight="1">
       <c r="D130" s="302"/>
       <c r="E130" s="342" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F130" s="303" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="131" spans="4:6" ht="15.75" customHeight="1">
       <c r="D131" s="302"/>
       <c r="E131" s="338" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F131" s="431" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="132" spans="4:6" ht="15.75" customHeight="1">
       <c r="D132" s="309"/>
       <c r="E132" s="338" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F132" s="303" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="133" spans="4:6" ht="15.75" customHeight="1">
       <c r="D133" s="302" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E133" s="345" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F133" s="303" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="134" spans="4:6" ht="15.75" customHeight="1">
       <c r="D134" s="302"/>
       <c r="E134" s="345" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F134" s="303" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="135" spans="4:6" ht="15.75" customHeight="1">
+      <c r="D135" s="437"/>
+      <c r="E135" s="345" t="s">
         <v>1056</v>
       </c>
-      <c r="F134" s="303" t="s">
+      <c r="F135" s="303" t="s">
         <v>1054</v>
-      </c>
-    </row>
-    <row r="135" spans="4:6" ht="15.75" customHeight="1">
-      <c r="D135" s="441"/>
-      <c r="E135" s="345" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F135" s="303" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="136" spans="4:6" ht="15.75" customHeight="1">
       <c r="D136" s="302" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E136" s="345" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F136" s="303" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="137" spans="4:6" ht="15.75" customHeight="1">
       <c r="D137" s="302"/>
       <c r="E137" s="345" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F137" s="303" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="138" spans="4:6" ht="15.75" customHeight="1">
+      <c r="D138" s="436"/>
+      <c r="E138" s="345" t="s">
         <v>1056</v>
       </c>
-      <c r="F137" s="303" t="s">
+      <c r="F138" s="303" t="s">
         <v>1054</v>
-      </c>
-    </row>
-    <row r="138" spans="4:6" ht="15.75" customHeight="1">
-      <c r="D138" s="440"/>
-      <c r="E138" s="345" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F138" s="303" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="139" spans="4:6" ht="15.75" customHeight="1">
       <c r="D139" s="349" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E139" s="334" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F139" s="438" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="140" spans="4:6" ht="15.75" customHeight="1">
+      <c r="D140" s="439"/>
+      <c r="E140" s="334" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F140" s="438" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="141" spans="4:6" ht="15.75" customHeight="1">
+      <c r="D141" s="442"/>
+      <c r="E141" s="334" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F141" s="438" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="142" spans="4:6" ht="15.75" customHeight="1">
+      <c r="D142" s="442"/>
+      <c r="E142" s="334" t="s">
         <v>1083</v>
       </c>
-      <c r="F139" s="442" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="140" spans="4:6" ht="15.75" customHeight="1">
-      <c r="D140" s="443"/>
-      <c r="E140" s="334" t="s">
-        <v>1067</v>
-      </c>
-      <c r="F140" s="442" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="141" spans="4:6" ht="15.75" customHeight="1">
-      <c r="D141" s="446"/>
-      <c r="E141" s="334" t="s">
-        <v>1068</v>
-      </c>
-      <c r="F141" s="442" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="142" spans="4:6" ht="15.75" customHeight="1">
-      <c r="D142" s="446"/>
-      <c r="E142" s="334" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F142" s="444" t="s">
-        <v>1071</v>
+      <c r="F142" s="440" t="s">
+        <v>1070</v>
       </c>
     </row>
     <row r="143" spans="4:6" ht="15.75" customHeight="1">
-      <c r="D143" s="446"/>
+      <c r="D143" s="442"/>
       <c r="E143" s="334" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F143" s="444" t="s">
-        <v>1070</v>
+        <v>1072</v>
+      </c>
+      <c r="F143" s="440" t="s">
+        <v>1069</v>
       </c>
     </row>
     <row r="144" spans="4:6" ht="15.75" customHeight="1">
       <c r="D144" s="336"/>
       <c r="E144" s="334" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F144" s="444" t="s">
-        <v>1072</v>
+        <v>1073</v>
+      </c>
+      <c r="F144" s="440" t="s">
+        <v>1071</v>
       </c>
     </row>
     <row r="145" spans="4:6" ht="15.75" customHeight="1">
       <c r="D145" s="349" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E145" s="334" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F145" s="444" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F145" s="440" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="146" spans="4:6" ht="15.75" customHeight="1">
+      <c r="D146" s="439"/>
+      <c r="E146" s="334" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F146" s="440" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="147" spans="4:6" ht="15.75" customHeight="1">
+      <c r="D147" s="441"/>
+      <c r="E147" s="334" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F147" s="440" t="s">
         <v>1071</v>
-      </c>
-    </row>
-    <row r="146" spans="4:6" ht="15.75" customHeight="1">
-      <c r="D146" s="443"/>
-      <c r="E146" s="334" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F146" s="444" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="147" spans="4:6" ht="15.75" customHeight="1">
-      <c r="D147" s="445"/>
-      <c r="E147" s="334" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F147" s="444" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="148" spans="4:6" ht="15.75" customHeight="1">
       <c r="D148" s="306" t="s">
-        <v>795</v>
-      </c>
-      <c r="E148" s="448" t="s">
-        <v>1087</v>
-      </c>
-      <c r="F148" s="449" t="s">
+        <v>794</v>
+      </c>
+      <c r="E148" s="443" t="s">
         <v>1086</v>
+      </c>
+      <c r="F148" s="444" t="s">
+        <v>1085</v>
       </c>
     </row>
     <row r="149" spans="4:6" ht="15.75" customHeight="1">
       <c r="D149" s="302"/>
-      <c r="E149" s="450" t="s">
-        <v>1088</v>
-      </c>
-      <c r="F149" s="451" t="s">
-        <v>1051</v>
+      <c r="E149" s="445" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F149" s="446" t="s">
+        <v>1050</v>
       </c>
     </row>
     <row r="150" spans="4:6" ht="15.75" customHeight="1">
       <c r="D150" s="302"/>
-      <c r="E150" s="448" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F150" s="455" t="s">
+      <c r="E150" s="443" t="s">
         <v>1090</v>
+      </c>
+      <c r="F150" s="450" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="151" spans="4:6" ht="15.75" customHeight="1">
       <c r="D151" s="304"/>
-      <c r="E151" s="448" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F151" s="452" t="s">
-        <v>1089</v>
+      <c r="E151" s="443" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F151" s="447" t="s">
+        <v>1088</v>
       </c>
     </row>
     <row r="152" spans="4:6" ht="15.75" customHeight="1">
       <c r="D152" s="306" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E152" s="345" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F152" s="456" t="s">
-        <v>1021</v>
+        <v>1091</v>
+      </c>
+      <c r="F152" s="451" t="s">
+        <v>1020</v>
       </c>
     </row>
     <row r="153" spans="4:6" ht="15.75" customHeight="1">
       <c r="D153" s="302"/>
       <c r="E153" s="345" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F153" s="453" t="s">
-        <v>1093</v>
+        <v>1022</v>
+      </c>
+      <c r="F153" s="448" t="s">
+        <v>1092</v>
       </c>
     </row>
     <row r="154" spans="4:6" ht="15.75" customHeight="1">
       <c r="D154" s="302"/>
       <c r="E154" s="345" t="s">
-        <v>1094</v>
-      </c>
-      <c r="F154" s="456" t="s">
-        <v>1024</v>
+        <v>1093</v>
+      </c>
+      <c r="F154" s="451" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="155" spans="4:6" ht="15.75" customHeight="1">
       <c r="D155" s="331"/>
       <c r="E155" s="345" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F155" s="456" t="s">
-        <v>1095</v>
+        <v>1025</v>
+      </c>
+      <c r="F155" s="451" t="s">
+        <v>1094</v>
       </c>
     </row>
     <row r="156" spans="4:6" ht="15.75" customHeight="1">
       <c r="D156" s="331"/>
       <c r="E156" s="345" t="s">
-        <v>1097</v>
-      </c>
-      <c r="F156" s="454" t="s">
         <v>1096</v>
+      </c>
+      <c r="F156" s="449" t="s">
+        <v>1095</v>
       </c>
     </row>
     <row r="157" spans="4:6" ht="15.75" customHeight="1">
       <c r="D157" s="331"/>
       <c r="E157" s="345" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F157" s="453" t="s">
-        <v>1099</v>
+        <v>1031</v>
+      </c>
+      <c r="F157" s="448" t="s">
+        <v>1098</v>
       </c>
     </row>
     <row r="158" spans="4:6" ht="15.75" customHeight="1">
       <c r="D158" s="331"/>
       <c r="E158" s="345" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F158" s="453" t="s">
-        <v>1100</v>
+        <v>1032</v>
+      </c>
+      <c r="F158" s="448" t="s">
+        <v>1099</v>
       </c>
     </row>
     <row r="159" spans="4:6" ht="15.75" customHeight="1">
       <c r="D159" s="331"/>
       <c r="E159" s="345" t="s">
-        <v>1104</v>
-      </c>
-      <c r="F159" s="456" t="s">
-        <v>1036</v>
+        <v>1103</v>
+      </c>
+      <c r="F159" s="451" t="s">
+        <v>1035</v>
       </c>
     </row>
     <row r="160" spans="4:6" ht="15.75" customHeight="1">
       <c r="D160" s="331"/>
       <c r="E160" s="345" t="s">
-        <v>1038</v>
-      </c>
-      <c r="F160" s="456" t="s">
         <v>1037</v>
+      </c>
+      <c r="F160" s="451" t="s">
+        <v>1036</v>
       </c>
     </row>
     <row r="161" spans="4:6" ht="15.75" customHeight="1">
       <c r="D161" s="331"/>
       <c r="E161" s="345" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F161" s="456" t="s">
         <v>1042</v>
+      </c>
+      <c r="F161" s="451" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="162" spans="4:6" ht="15.75" customHeight="1">
       <c r="D162" s="331"/>
       <c r="E162" s="345" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F162" s="454" t="s">
-        <v>1105</v>
+        <v>1048</v>
+      </c>
+      <c r="F162" s="449" t="s">
+        <v>1104</v>
       </c>
     </row>
     <row r="163" spans="4:6" ht="15.75" customHeight="1">
       <c r="D163" s="331"/>
       <c r="E163" s="345" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F163" s="457" t="s">
-        <v>1106</v>
+        <v>1047</v>
+      </c>
+      <c r="F163" s="452" t="s">
+        <v>1105</v>
       </c>
     </row>
     <row r="164" spans="4:6" ht="15.75" customHeight="1">
       <c r="D164" s="331"/>
       <c r="E164" s="345" t="s">
-        <v>1110</v>
-      </c>
-      <c r="F164" s="457" t="s">
-        <v>1112</v>
+        <v>1109</v>
+      </c>
+      <c r="F164" s="452" t="s">
+        <v>1111</v>
       </c>
     </row>
     <row r="165" spans="4:6" ht="15.75" customHeight="1">
       <c r="D165" s="332"/>
       <c r="E165" s="345" t="s">
-        <v>1111</v>
-      </c>
-      <c r="F165" s="439" t="s">
-        <v>1052</v>
+        <v>1110</v>
+      </c>
+      <c r="F165" s="435" t="s">
+        <v>1051</v>
       </c>
     </row>
     <row r="166" spans="4:6" ht="15.75" customHeight="1">
       <c r="D166" s="306" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E166" s="345" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F166" s="456" t="s">
-        <v>1021</v>
+        <v>1091</v>
+      </c>
+      <c r="F166" s="451" t="s">
+        <v>1020</v>
       </c>
     </row>
     <row r="167" spans="4:6" ht="15.75" customHeight="1">
       <c r="D167" s="302"/>
       <c r="E167" s="345" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F167" s="453" t="s">
-        <v>1093</v>
+        <v>1022</v>
+      </c>
+      <c r="F167" s="448" t="s">
+        <v>1092</v>
       </c>
     </row>
     <row r="168" spans="4:6" ht="15.75" customHeight="1">
       <c r="D168" s="302"/>
       <c r="E168" s="345" t="s">
-        <v>1094</v>
-      </c>
-      <c r="F168" s="456" t="s">
-        <v>1024</v>
+        <v>1093</v>
+      </c>
+      <c r="F168" s="451" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="169" spans="4:6" ht="15.75" customHeight="1">
       <c r="D169" s="331"/>
       <c r="E169" s="345" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F169" s="456" t="s">
-        <v>1095</v>
+        <v>1025</v>
+      </c>
+      <c r="F169" s="451" t="s">
+        <v>1094</v>
       </c>
     </row>
     <row r="170" spans="4:6" ht="15.75" customHeight="1">
       <c r="D170" s="331"/>
       <c r="E170" s="345" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F170" s="449" t="s">
         <v>1097</v>
-      </c>
-      <c r="F170" s="454" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="171" spans="4:6" ht="15.75" customHeight="1">
       <c r="D171" s="331"/>
       <c r="E171" s="345" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F171" s="453" t="s">
-        <v>1099</v>
+        <v>1031</v>
+      </c>
+      <c r="F171" s="448" t="s">
+        <v>1098</v>
       </c>
     </row>
     <row r="172" spans="4:6" ht="15.75" customHeight="1">
       <c r="D172" s="331"/>
       <c r="E172" s="345" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F172" s="453" t="s">
-        <v>1100</v>
+        <v>1032</v>
+      </c>
+      <c r="F172" s="448" t="s">
+        <v>1099</v>
       </c>
     </row>
     <row r="173" spans="4:6" ht="15.75" customHeight="1">
       <c r="D173" s="331"/>
       <c r="E173" s="345" t="s">
-        <v>1104</v>
-      </c>
-      <c r="F173" s="456" t="s">
-        <v>1036</v>
+        <v>1103</v>
+      </c>
+      <c r="F173" s="451" t="s">
+        <v>1035</v>
       </c>
     </row>
     <row r="174" spans="4:6" ht="15.75" customHeight="1">
       <c r="D174" s="331"/>
       <c r="E174" s="345" t="s">
-        <v>1038</v>
-      </c>
-      <c r="F174" s="456" t="s">
         <v>1037</v>
+      </c>
+      <c r="F174" s="451" t="s">
+        <v>1036</v>
       </c>
     </row>
     <row r="175" spans="4:6" ht="15.75" customHeight="1">
       <c r="D175" s="331"/>
       <c r="E175" s="345" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F175" s="456" t="s">
         <v>1042</v>
+      </c>
+      <c r="F175" s="451" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="176" spans="4:6" ht="15.75" customHeight="1">
       <c r="D176" s="331"/>
       <c r="E176" s="345" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F176" s="454" t="s">
-        <v>1105</v>
+        <v>1048</v>
+      </c>
+      <c r="F176" s="449" t="s">
+        <v>1104</v>
       </c>
     </row>
     <row r="177" spans="4:6" ht="15.75" customHeight="1">
       <c r="D177" s="331"/>
       <c r="E177" s="345" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F177" s="457" t="s">
-        <v>1106</v>
+        <v>1047</v>
+      </c>
+      <c r="F177" s="452" t="s">
+        <v>1105</v>
       </c>
     </row>
     <row r="178" spans="4:6" ht="15.75" customHeight="1">
       <c r="D178" s="331"/>
       <c r="E178" s="345" t="s">
-        <v>1110</v>
-      </c>
-      <c r="F178" s="457" t="s">
-        <v>1112</v>
+        <v>1109</v>
+      </c>
+      <c r="F178" s="452" t="s">
+        <v>1111</v>
       </c>
     </row>
     <row r="179" spans="4:6" ht="15.75" customHeight="1">
       <c r="D179" s="332"/>
       <c r="E179" s="345" t="s">
-        <v>1111</v>
-      </c>
-      <c r="F179" s="439" t="s">
-        <v>1052</v>
+        <v>1110</v>
+      </c>
+      <c r="F179" s="435" t="s">
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
